--- a/_25 sentences new.xlsx
+++ b/_25 sentences new.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="182">
   <si>
     <t>Audio</t>
   </si>
@@ -34,7 +34,8 @@
     <t>Malayalam Wrod</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1I6HHj5yty_vhtKh6NAY8u2HGamhwsfJu/view?usp=sharing</t>
+    <t xml:space="preserve">DATA/fleurs_en_test_1957.wav
+</t>
   </si>
   <si>
     <t>he referred to the rumors as political chatter and silliness</t>
@@ -59,7 +60,8 @@
     <t>രാഷ്ട്രീയ സംഭാഷണവും മന്ദബുദ്ധിയും</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1kf-LweoIC5ULmZLnrquJQixj08aAwAoq/view?usp=sharing</t>
+    <t xml:space="preserve">DATA/fleurs_en_train_611.wav
+</t>
   </si>
   <si>
     <t>computers today are used to manipulate pictures and videos</t>
@@ -81,7 +83,7 @@
     <t>ചിത്രങ്ങളും വീഡിയോകളും കൈകാര്യം ചെയ്യാനാണ്</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1Qks7-46fvfAEvsXsMgehhCLtPLTKp8Jq/view?usp=sharing</t>
+    <t>DATA/fleurs_en_validation_1531.wav</t>
   </si>
   <si>
     <t>the east african islands are in the indian ocean off the eastern coast of africa</t>
@@ -103,7 +105,7 @@
     <t xml:space="preserve">ഇന്ത്യൻ സമുദ്രത്തിലാണ് </t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1jVTHXfcipTM9BCfOLmtFOQofinzdsklD/view?usp=sharing</t>
+    <t>DATA/fleurs_en_train_493.wav</t>
   </si>
   <si>
     <t>the civilisation flourished in the basins of the indus river wherefore it derives its name</t>
@@ -125,7 +127,7 @@
     <t>സിന്ധു നദീതടങ്ങളിലായതിനാലാണ്</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/19J8mUOJ-0-6F63CNblh2meLPVm4ytNre/view?usp=sharing</t>
+    <t>DATA/fleurs_en_train_352.wav</t>
   </si>
   <si>
     <t>the steel needle floats on top of the water because of surface tension</t>
@@ -147,7 +149,7 @@
     <t xml:space="preserve">ഉപരിതല മർദ്ദം കാരണമായാണ് </t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1LNbPoIsYcpZhRpyVAx8T0kTxQ8XjmxUV/view?usp=sharing</t>
+    <t>DATA/fleurs_en_train_282.wav</t>
   </si>
   <si>
     <t>in berlin police estimated 6,500 protestors</t>
@@ -169,7 +171,7 @@
     <t xml:space="preserve"> പ്രതിഷേധക്കാരെയാണ്</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1mjGoQgXfBqwAoY_7ppzgGnHsBzooA0Mv/view?usp=sharing</t>
+    <t>DATA/fleurs_en_train_86.wav</t>
   </si>
   <si>
     <t>pittman suggested that conditions wouldn't improve until sometime next week</t>
@@ -191,7 +193,7 @@
     <t xml:space="preserve">ഈ അവസ്ഥ മെച്ചപ്പെടില്ല </t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1sXpWQCfT6fQ2AKhdHs2oDEBw2JsBp926/view?usp=sharing</t>
+    <t>DATA/fleurs_en_test_1762.wav</t>
   </si>
   <si>
     <t>the disease is carried by pigs which then migrates to humans through mosquitos</t>
@@ -212,7 +214,7 @@
     <t>പന്നികളാണ്</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1T_2ifv8NjNI1qh8VHb3Fsq4zuV1bpdg3/view?usp=sharing</t>
+    <t>DATA/fleurs_en_train_1395.wav</t>
   </si>
   <si>
     <t>your local telephone service provider should be able to give more information about connecting to this service</t>
@@ -234,7 +236,7 @@
     <t>വിവരങ്ങൾ നൽകാൻ കഴിയേണ്ടതാണ്</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1GLK6E-QcT7MYha7kOaXUFcLJ_R6SMbjv/view?usp=sharing</t>
+    <t>DATA/fleurs_en_train_190.wav</t>
   </si>
   <si>
     <t>the typhoon is estimated to be moving toward china at eleven kph</t>
@@ -256,7 +258,7 @@
     <t xml:space="preserve">ചൈനയിലേക്ക് നീങ്ങുമെന്നാണ് </t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1vBGgAAKLB9pRn7PW29F6gh4Ql-F7EeEm/view?usp=sharing</t>
+    <t>DATA/fleurs_en_train_307.wav</t>
   </si>
   <si>
     <t>the cause of death was announced as intrahepatic bile duct cancer</t>
@@ -278,7 +280,7 @@
     <t>ഇൻട്രാഹെപ്പറ്റിക് പിത്തനാളി അർബുദമാണ്</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1EG8NuF7D4y1GVBJOkmPdFjWiVZBenyr-/view?usp=sharing</t>
+    <t>DATA/fleurs_en_validation_1548.wav</t>
   </si>
   <si>
     <t>when you call someone who is thousands of miles away you are using a satellite</t>
@@ -300,7 +302,7 @@
     <t>ഒരു ഉപഗ്രഹമാണ്</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1xs-oxVhO-jistWyQ_Uwlke0WEpMTh-18/view?usp=sharing</t>
+    <t>DATA/fleurs_en_test_1962.wav</t>
   </si>
   <si>
     <t>the ph level is indicated by the amount of hydrogen the h in ph ions in the tested chemical</t>
@@ -322,7 +324,7 @@
     <t>എച്ച് അളവാണ്</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1gzLdcQje5g27OMAHkJXSFUWwpnxX0Vze/view?usp=sharing</t>
+    <t>DATA/fleurs_en_validation_1615.wav</t>
   </si>
   <si>
     <t>thousands of years ago a man called aristarchus said that the solar system moved around the sun</t>
@@ -344,7 +346,7 @@
     <t>സൂര്യനുചുറ്റുമാണ്</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1T-To-WPZnOorCTKMRh62JyhAoQsMsjA9/view?usp=drive_link</t>
+    <t>DATA/fleurs_en_validation_1567.wav</t>
   </si>
   <si>
     <t>the largest tournament of the year takes place in december at the polo fields in las cañitas</t>
@@ -366,7 +368,7 @@
     <t>പോളോ ഫീൽഡ്സിലാണ്</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1Z9I_QAo0ZNSbb3cg6o3vvfEX8NLZytgv/view?usp=sharing</t>
+    <t>DATA/fleurs_en_train_405.wav</t>
   </si>
   <si>
     <t>german submarines were called u-boats the germans were very good at navigating and operating their submarines</t>
@@ -388,7 +390,7 @@
     <t>യു-ബോട്ടുകൾ</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1bMxLjLHJC32HHMhGKwDtTQm_gEofHPbb/view?usp=sharing</t>
+    <t>DATA/fleurs_en_train_378.wav</t>
   </si>
   <si>
     <t>the outer-part we see when we look at the sun is called the photosphere which means ball of light</t>
@@ -409,7 +411,7 @@
     <t>പ്രകാശത്തിന്റെ പന്ത്</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/10OWc66JHO7vvUqr6JuIJq6czQPCjDZP3/view?usp=sharing</t>
+    <t>DATA/fleurs_en_train_1461.wav</t>
   </si>
   <si>
     <t>wagonways were built in england as early as the 16th century</t>
@@ -431,7 +433,7 @@
     <t>പതിനാറാം നൂറ്റാണ്ടിലാണ്</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1XaoK9o0mSaWFFF1QUNsD3pKISrSCsYG8/view?usp=sharing</t>
+    <t>DATA/fleurs_en_train_1017.wav</t>
   </si>
   <si>
     <t>the rock band was due to tour the united states and canada until september 16</t>
@@ -453,9 +455,6 @@
     <t>അമേരിക്കയിലും കാനഡയിലുമാണ്</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1fVfbCbe61d6BqBy4mzoAxJvE7Z1--ocu/view?usp=sharing</t>
-  </si>
-  <si>
     <t>the water molecules make an invisible skin on the water's surface that allows things like the needle to float on top of the water</t>
   </si>
   <si>
@@ -475,7 +474,7 @@
     <t>ജല തൻമാത്രകൾ ജലത്തിൻ്റെ ഉപരിതലത്തിനു മേൽ അദൃശ്യമായ ഒരു പാട സൃഷ്ടിക്കുന്നു</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1UO9jreNeNLTvfwEum1IvMvu1l_e6_rra/view?usp=sharing</t>
+    <t>DATA/fleurs_en_train_359.wav</t>
   </si>
   <si>
     <t>they do this by emitting a tiny particle of light called a photon</t>
@@ -497,7 +496,7 @@
     <t>പുറത്തുവിട്ടാണ്</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1ZqTHBMGRfJ8N013kGUc8ABNDNznY_l1J/view?usp=sharing</t>
+    <t>DATA/fleurs_en_train_484.wav</t>
   </si>
   <si>
     <t>followers pursue certain ways of living or practices that are intended to nurture those experiences</t>
@@ -519,7 +518,7 @@
     <t>പരിപോഷിപ്പിക്കാൻ ഉദ്ദേശിച്ചുള്ളതാണ്</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1cBkOPkteeGGd2JW14dU_y7tMNunVSg8j/view?usp=sharing</t>
+    <t>DATA/fleurs_en_train_1430.wav</t>
   </si>
   <si>
     <t>many paleontologists today believe that one group of dinosaurs survived and is alive today we call them birds</t>
@@ -541,7 +540,7 @@
     <t xml:space="preserve">ഇപ്പോഴും ജീവിച്ചിരിക്കുന്നുണ്ടെന്നുമാണ് </t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1M2tQDnDt5Py-IEZMxE9tR2bDFEWlCZOg/view?usp=sharing</t>
+    <t>DATA/fleurs_en_train_308.wav</t>
   </si>
   <si>
     <t>he died in osaka on tuesday</t>
@@ -563,7 +562,7 @@
     <t>ചൊവ്വാഴ്ചയാണ്</t>
   </si>
   <si>
-    <t>https://drive.google.com/file/d/1J9WCg6E8YbrblgJK-JJhiNErf26wzB1X/view?usp=sharing</t>
+    <t>DATA/fleurs_en_train_4.wav</t>
   </si>
   <si>
     <t>the pilot was identified as squadron leader dilokrit pattavee</t>
@@ -589,7 +588,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -620,11 +619,6 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10.0"/>
-      <color rgb="FF0000FF"/>
     </font>
     <font>
       <u/>
@@ -691,7 +685,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -713,10 +707,7 @@
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -725,7 +716,7 @@
     <xf borderId="1" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="2" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="2" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
     <xf borderId="2" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -740,10 +731,10 @@
     <xf borderId="3" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="bottom" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -1150,7 +1141,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="7" t="s">
+      <c r="A8" s="3" t="s">
         <v>50</v>
       </c>
       <c r="B8" s="4" t="s">
@@ -1228,7 +1219,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="7" t="s">
+      <c r="A11" s="3" t="s">
         <v>71</v>
       </c>
       <c r="B11" s="4" t="s">
@@ -1254,7 +1245,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="7" t="s">
+      <c r="A12" s="3" t="s">
         <v>78</v>
       </c>
       <c r="B12" s="4" t="s">
@@ -1280,7 +1271,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="s">
+      <c r="A13" s="3" t="s">
         <v>85</v>
       </c>
       <c r="B13" s="4" t="s">
@@ -1306,7 +1297,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="7" t="s">
+      <c r="A14" s="3" t="s">
         <v>92</v>
       </c>
       <c r="B14" s="4" t="s">
@@ -1332,7 +1323,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="7" t="s">
+      <c r="A15" s="3" t="s">
         <v>99</v>
       </c>
       <c r="B15" s="4" t="s">
@@ -1410,13 +1401,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="8" t="s">
+      <c r="A18" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="B18" s="9" t="s">
+      <c r="B18" s="8" t="s">
         <v>121</v>
       </c>
-      <c r="C18" s="9" t="s">
+      <c r="C18" s="8" t="s">
         <v>122</v>
       </c>
       <c r="D18" s="5" t="s">
@@ -1436,7 +1427,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="7" t="s">
+      <c r="A19" s="3" t="s">
         <v>127</v>
       </c>
       <c r="B19" s="4" t="s">
@@ -1488,2873 +1479,2873 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="7" t="s">
+      <c r="A21" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="B21" s="4" t="s">
         <v>141</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="C21" s="4" t="s">
         <v>142</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="D21" s="5" t="s">
         <v>143</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="E21" s="5" t="s">
         <v>144</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>145</v>
       </c>
       <c r="F21" s="6" t="s">
         <v>12</v>
       </c>
       <c r="G21" s="5" t="s">
+        <v>145</v>
+      </c>
+      <c r="H21" s="5" t="s">
         <v>146</v>
-      </c>
-      <c r="H21" s="5" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="B22" s="4" t="s">
         <v>148</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="C22" s="4" t="s">
         <v>149</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="D22" s="5" t="s">
         <v>150</v>
       </c>
-      <c r="D22" s="5" t="s">
+      <c r="E22" s="5" t="s">
         <v>151</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>152</v>
       </c>
       <c r="F22" s="6" t="s">
         <v>12</v>
       </c>
       <c r="G22" s="5" t="s">
+        <v>152</v>
+      </c>
+      <c r="H22" s="5" t="s">
         <v>153</v>
-      </c>
-      <c r="H22" s="5" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="B23" s="4" t="s">
         <v>155</v>
       </c>
-      <c r="B23" s="4" t="s">
+      <c r="C23" s="9" t="s">
         <v>156</v>
       </c>
-      <c r="C23" s="10" t="s">
+      <c r="D23" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="D23" s="5" t="s">
+      <c r="E23" s="5" t="s">
         <v>158</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>159</v>
       </c>
       <c r="F23" s="6" t="s">
         <v>12</v>
       </c>
       <c r="G23" s="5" t="s">
+        <v>159</v>
+      </c>
+      <c r="H23" s="5" t="s">
         <v>160</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>161</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="B24" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="B24" s="4" t="s">
+      <c r="C24" s="4" t="s">
         <v>163</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="D24" s="5" t="s">
         <v>164</v>
       </c>
-      <c r="D24" s="5" t="s">
+      <c r="E24" s="5" t="s">
         <v>165</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>166</v>
       </c>
       <c r="F24" s="6" t="s">
         <v>12</v>
       </c>
       <c r="G24" s="5" t="s">
+        <v>166</v>
+      </c>
+      <c r="H24" s="5" t="s">
         <v>167</v>
-      </c>
-      <c r="H24" s="5" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="B25" s="4" t="s">
         <v>169</v>
       </c>
-      <c r="B25" s="4" t="s">
+      <c r="C25" s="4" t="s">
         <v>170</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="D25" s="5" t="s">
         <v>171</v>
       </c>
-      <c r="D25" s="5" t="s">
+      <c r="E25" s="5" t="s">
         <v>172</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>173</v>
       </c>
       <c r="F25" s="6" t="s">
         <v>12</v>
       </c>
       <c r="G25" s="5" t="s">
+        <v>173</v>
+      </c>
+      <c r="H25" s="5" t="s">
         <v>174</v>
       </c>
-      <c r="H25" s="5" t="s">
+    </row>
+    <row r="26">
+      <c r="A26" s="10" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="11" t="s">
+      <c r="B26" s="11" t="s">
         <v>176</v>
       </c>
-      <c r="B26" s="12" t="s">
+      <c r="C26" s="11" t="s">
         <v>177</v>
       </c>
-      <c r="C26" s="12" t="s">
+      <c r="D26" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="D26" s="13" t="s">
+      <c r="E26" s="12" t="s">
         <v>179</v>
-      </c>
-      <c r="E26" s="13" t="s">
-        <v>180</v>
       </c>
       <c r="F26" s="6" t="s">
         <v>12</v>
       </c>
       <c r="G26" s="5" t="s">
+        <v>180</v>
+      </c>
+      <c r="H26" s="5" t="s">
         <v>181</v>
       </c>
-      <c r="H26" s="5" t="s">
-        <v>182</v>
-      </c>
     </row>
     <row r="27">
-      <c r="A27" s="14">
+      <c r="A27" s="13">
         <f>COUNTA(A2:A26)</f>
         <v>25</v>
       </c>
-      <c r="B27" s="15"/>
-      <c r="C27" s="15"/>
-      <c r="D27" s="15"/>
-      <c r="E27" s="15"/>
-      <c r="F27" s="15"/>
-      <c r="G27" s="15"/>
-      <c r="H27" s="15"/>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+      <c r="G27" s="14"/>
+      <c r="H27" s="14"/>
     </row>
     <row r="28">
-      <c r="E28" s="16"/>
+      <c r="E28" s="15"/>
     </row>
     <row r="29">
-      <c r="E29" s="17"/>
+      <c r="E29" s="16"/>
     </row>
     <row r="30">
-      <c r="E30" s="17"/>
+      <c r="E30" s="16"/>
     </row>
     <row r="31">
-      <c r="E31" s="17"/>
+      <c r="E31" s="16"/>
     </row>
     <row r="32">
-      <c r="E32" s="17"/>
+      <c r="E32" s="16"/>
     </row>
     <row r="33">
-      <c r="E33" s="17"/>
+      <c r="E33" s="16"/>
     </row>
     <row r="34">
-      <c r="E34" s="17"/>
+      <c r="E34" s="16"/>
     </row>
     <row r="35">
-      <c r="E35" s="17"/>
+      <c r="E35" s="16"/>
     </row>
     <row r="36">
-      <c r="E36" s="17"/>
+      <c r="E36" s="16"/>
     </row>
     <row r="37">
-      <c r="E37" s="17"/>
+      <c r="E37" s="16"/>
     </row>
     <row r="38">
-      <c r="E38" s="17"/>
+      <c r="E38" s="16"/>
     </row>
     <row r="39">
-      <c r="E39" s="17"/>
+      <c r="E39" s="16"/>
     </row>
     <row r="40">
-      <c r="E40" s="17"/>
+      <c r="E40" s="16"/>
     </row>
     <row r="41">
-      <c r="E41" s="17"/>
+      <c r="E41" s="16"/>
     </row>
     <row r="42">
-      <c r="E42" s="17"/>
+      <c r="E42" s="16"/>
     </row>
     <row r="43">
-      <c r="E43" s="17"/>
+      <c r="E43" s="16"/>
     </row>
     <row r="44">
-      <c r="E44" s="17"/>
+      <c r="E44" s="16"/>
     </row>
     <row r="45">
-      <c r="E45" s="17"/>
+      <c r="E45" s="16"/>
     </row>
     <row r="46">
-      <c r="E46" s="17"/>
+      <c r="E46" s="16"/>
     </row>
     <row r="47">
-      <c r="E47" s="17"/>
+      <c r="E47" s="16"/>
     </row>
     <row r="48">
-      <c r="E48" s="17"/>
+      <c r="E48" s="16"/>
     </row>
     <row r="49">
-      <c r="E49" s="17"/>
+      <c r="E49" s="16"/>
     </row>
     <row r="50">
-      <c r="E50" s="17"/>
+      <c r="E50" s="16"/>
     </row>
     <row r="51">
-      <c r="E51" s="17"/>
+      <c r="E51" s="16"/>
     </row>
     <row r="52">
-      <c r="E52" s="17"/>
+      <c r="E52" s="16"/>
     </row>
     <row r="53">
-      <c r="E53" s="17"/>
+      <c r="E53" s="16"/>
     </row>
     <row r="54">
-      <c r="E54" s="17"/>
+      <c r="E54" s="16"/>
     </row>
     <row r="55">
-      <c r="E55" s="17"/>
+      <c r="E55" s="16"/>
     </row>
     <row r="56">
-      <c r="E56" s="17"/>
+      <c r="E56" s="16"/>
     </row>
     <row r="57">
-      <c r="E57" s="17"/>
+      <c r="E57" s="16"/>
     </row>
     <row r="58">
-      <c r="E58" s="17"/>
+      <c r="E58" s="16"/>
     </row>
     <row r="59">
-      <c r="E59" s="17"/>
+      <c r="E59" s="16"/>
     </row>
     <row r="60">
-      <c r="E60" s="17"/>
+      <c r="E60" s="16"/>
     </row>
     <row r="61">
-      <c r="E61" s="17"/>
+      <c r="E61" s="16"/>
     </row>
     <row r="62">
-      <c r="E62" s="17"/>
+      <c r="E62" s="16"/>
     </row>
     <row r="63">
-      <c r="E63" s="17"/>
+      <c r="E63" s="16"/>
     </row>
     <row r="64">
-      <c r="E64" s="17"/>
+      <c r="E64" s="16"/>
     </row>
     <row r="65">
-      <c r="E65" s="17"/>
+      <c r="E65" s="16"/>
     </row>
     <row r="66">
-      <c r="E66" s="17"/>
+      <c r="E66" s="16"/>
     </row>
     <row r="67">
-      <c r="E67" s="17"/>
+      <c r="E67" s="16"/>
     </row>
     <row r="68">
-      <c r="E68" s="17"/>
+      <c r="E68" s="16"/>
     </row>
     <row r="69">
-      <c r="E69" s="17"/>
+      <c r="E69" s="16"/>
     </row>
     <row r="70">
-      <c r="E70" s="17"/>
+      <c r="E70" s="16"/>
     </row>
     <row r="71">
-      <c r="E71" s="17"/>
+      <c r="E71" s="16"/>
     </row>
     <row r="72">
-      <c r="E72" s="17"/>
+      <c r="E72" s="16"/>
     </row>
     <row r="73">
-      <c r="E73" s="17"/>
+      <c r="E73" s="16"/>
     </row>
     <row r="74">
-      <c r="E74" s="17"/>
+      <c r="E74" s="16"/>
     </row>
     <row r="75">
-      <c r="E75" s="17"/>
+      <c r="E75" s="16"/>
     </row>
     <row r="76">
-      <c r="E76" s="17"/>
+      <c r="E76" s="16"/>
     </row>
     <row r="77">
-      <c r="E77" s="17"/>
+      <c r="E77" s="16"/>
     </row>
     <row r="78">
-      <c r="E78" s="17"/>
+      <c r="E78" s="16"/>
     </row>
     <row r="79">
-      <c r="E79" s="17"/>
+      <c r="E79" s="16"/>
     </row>
     <row r="80">
-      <c r="E80" s="17"/>
+      <c r="E80" s="16"/>
     </row>
     <row r="81">
-      <c r="E81" s="17"/>
+      <c r="E81" s="16"/>
     </row>
     <row r="82">
-      <c r="E82" s="17"/>
+      <c r="E82" s="16"/>
     </row>
     <row r="83">
-      <c r="E83" s="17"/>
+      <c r="E83" s="16"/>
     </row>
     <row r="84">
-      <c r="E84" s="17"/>
+      <c r="E84" s="16"/>
     </row>
     <row r="85">
-      <c r="E85" s="17"/>
+      <c r="E85" s="16"/>
     </row>
     <row r="86">
-      <c r="E86" s="17"/>
+      <c r="E86" s="16"/>
     </row>
     <row r="87">
-      <c r="E87" s="17"/>
+      <c r="E87" s="16"/>
     </row>
     <row r="88">
-      <c r="E88" s="17"/>
+      <c r="E88" s="16"/>
     </row>
     <row r="89">
-      <c r="E89" s="17"/>
+      <c r="E89" s="16"/>
     </row>
     <row r="90">
-      <c r="E90" s="17"/>
+      <c r="E90" s="16"/>
     </row>
     <row r="91">
-      <c r="E91" s="17"/>
+      <c r="E91" s="16"/>
     </row>
     <row r="92">
-      <c r="E92" s="17"/>
+      <c r="E92" s="16"/>
     </row>
     <row r="93">
-      <c r="E93" s="17"/>
+      <c r="E93" s="16"/>
     </row>
     <row r="94">
-      <c r="E94" s="17"/>
+      <c r="E94" s="16"/>
     </row>
     <row r="95">
-      <c r="E95" s="17"/>
+      <c r="E95" s="16"/>
     </row>
     <row r="96">
-      <c r="E96" s="17"/>
+      <c r="E96" s="16"/>
     </row>
     <row r="97">
-      <c r="E97" s="17"/>
+      <c r="E97" s="16"/>
     </row>
     <row r="98">
-      <c r="E98" s="17"/>
+      <c r="E98" s="16"/>
     </row>
     <row r="99">
-      <c r="E99" s="17"/>
+      <c r="E99" s="16"/>
     </row>
     <row r="100">
-      <c r="E100" s="17"/>
+      <c r="E100" s="16"/>
     </row>
     <row r="101">
-      <c r="E101" s="17"/>
+      <c r="E101" s="16"/>
     </row>
     <row r="102">
-      <c r="E102" s="17"/>
+      <c r="E102" s="16"/>
     </row>
     <row r="103">
-      <c r="E103" s="17"/>
+      <c r="E103" s="16"/>
     </row>
     <row r="104">
-      <c r="E104" s="17"/>
+      <c r="E104" s="16"/>
     </row>
     <row r="105">
-      <c r="E105" s="17"/>
+      <c r="E105" s="16"/>
     </row>
     <row r="106">
-      <c r="E106" s="17"/>
+      <c r="E106" s="16"/>
     </row>
     <row r="107">
-      <c r="E107" s="17"/>
+      <c r="E107" s="16"/>
     </row>
     <row r="108">
-      <c r="E108" s="17"/>
+      <c r="E108" s="16"/>
     </row>
     <row r="109">
-      <c r="E109" s="17"/>
+      <c r="E109" s="16"/>
     </row>
     <row r="110">
-      <c r="E110" s="17"/>
+      <c r="E110" s="16"/>
     </row>
     <row r="111">
-      <c r="E111" s="17"/>
+      <c r="E111" s="16"/>
     </row>
     <row r="112">
-      <c r="E112" s="17"/>
+      <c r="E112" s="16"/>
     </row>
     <row r="113">
-      <c r="E113" s="17"/>
+      <c r="E113" s="16"/>
     </row>
     <row r="114">
-      <c r="E114" s="17"/>
+      <c r="E114" s="16"/>
     </row>
     <row r="115">
-      <c r="E115" s="17"/>
+      <c r="E115" s="16"/>
     </row>
     <row r="116">
-      <c r="E116" s="17"/>
+      <c r="E116" s="16"/>
     </row>
     <row r="117">
-      <c r="E117" s="17"/>
+      <c r="E117" s="16"/>
     </row>
     <row r="118">
-      <c r="E118" s="17"/>
+      <c r="E118" s="16"/>
     </row>
     <row r="119">
-      <c r="E119" s="17"/>
+      <c r="E119" s="16"/>
     </row>
     <row r="120">
-      <c r="E120" s="17"/>
+      <c r="E120" s="16"/>
     </row>
     <row r="121">
-      <c r="E121" s="17"/>
+      <c r="E121" s="16"/>
     </row>
     <row r="122">
-      <c r="E122" s="17"/>
+      <c r="E122" s="16"/>
     </row>
     <row r="123">
-      <c r="E123" s="17"/>
+      <c r="E123" s="16"/>
     </row>
     <row r="124">
-      <c r="E124" s="17"/>
+      <c r="E124" s="16"/>
     </row>
     <row r="125">
-      <c r="E125" s="17"/>
+      <c r="E125" s="16"/>
     </row>
     <row r="126">
-      <c r="E126" s="17"/>
+      <c r="E126" s="16"/>
     </row>
     <row r="127">
-      <c r="E127" s="17"/>
+      <c r="E127" s="16"/>
     </row>
     <row r="128">
-      <c r="E128" s="17"/>
+      <c r="E128" s="16"/>
     </row>
     <row r="129">
-      <c r="E129" s="17"/>
+      <c r="E129" s="16"/>
     </row>
     <row r="130">
-      <c r="E130" s="17"/>
+      <c r="E130" s="16"/>
     </row>
     <row r="131">
-      <c r="E131" s="17"/>
+      <c r="E131" s="16"/>
     </row>
     <row r="132">
-      <c r="E132" s="17"/>
+      <c r="E132" s="16"/>
     </row>
     <row r="133">
-      <c r="E133" s="17"/>
+      <c r="E133" s="16"/>
     </row>
     <row r="134">
-      <c r="E134" s="17"/>
+      <c r="E134" s="16"/>
     </row>
     <row r="135">
-      <c r="E135" s="17"/>
+      <c r="E135" s="16"/>
     </row>
     <row r="136">
-      <c r="E136" s="17"/>
+      <c r="E136" s="16"/>
     </row>
     <row r="137">
-      <c r="E137" s="17"/>
+      <c r="E137" s="16"/>
     </row>
     <row r="138">
-      <c r="E138" s="17"/>
+      <c r="E138" s="16"/>
     </row>
     <row r="139">
-      <c r="E139" s="17"/>
+      <c r="E139" s="16"/>
     </row>
     <row r="140">
-      <c r="E140" s="17"/>
+      <c r="E140" s="16"/>
     </row>
     <row r="141">
-      <c r="E141" s="17"/>
+      <c r="E141" s="16"/>
     </row>
     <row r="142">
-      <c r="E142" s="17"/>
+      <c r="E142" s="16"/>
     </row>
     <row r="143">
-      <c r="E143" s="17"/>
+      <c r="E143" s="16"/>
     </row>
     <row r="144">
-      <c r="E144" s="17"/>
+      <c r="E144" s="16"/>
     </row>
     <row r="145">
-      <c r="E145" s="17"/>
+      <c r="E145" s="16"/>
     </row>
     <row r="146">
-      <c r="E146" s="17"/>
+      <c r="E146" s="16"/>
     </row>
     <row r="147">
-      <c r="E147" s="17"/>
+      <c r="E147" s="16"/>
     </row>
     <row r="148">
-      <c r="E148" s="17"/>
+      <c r="E148" s="16"/>
     </row>
     <row r="149">
-      <c r="E149" s="17"/>
+      <c r="E149" s="16"/>
     </row>
     <row r="150">
-      <c r="E150" s="17"/>
+      <c r="E150" s="16"/>
     </row>
     <row r="151">
-      <c r="E151" s="17"/>
+      <c r="E151" s="16"/>
     </row>
     <row r="152">
-      <c r="E152" s="17"/>
+      <c r="E152" s="16"/>
     </row>
     <row r="153">
-      <c r="E153" s="17"/>
+      <c r="E153" s="16"/>
     </row>
     <row r="154">
-      <c r="E154" s="17"/>
+      <c r="E154" s="16"/>
     </row>
     <row r="155">
-      <c r="E155" s="17"/>
+      <c r="E155" s="16"/>
     </row>
     <row r="156">
-      <c r="E156" s="17"/>
+      <c r="E156" s="16"/>
     </row>
     <row r="157">
-      <c r="E157" s="17"/>
+      <c r="E157" s="16"/>
     </row>
     <row r="158">
-      <c r="E158" s="17"/>
+      <c r="E158" s="16"/>
     </row>
     <row r="159">
-      <c r="E159" s="17"/>
+      <c r="E159" s="16"/>
     </row>
     <row r="160">
-      <c r="E160" s="17"/>
+      <c r="E160" s="16"/>
     </row>
     <row r="161">
-      <c r="E161" s="17"/>
+      <c r="E161" s="16"/>
     </row>
     <row r="162">
-      <c r="E162" s="17"/>
+      <c r="E162" s="16"/>
     </row>
     <row r="163">
-      <c r="E163" s="17"/>
+      <c r="E163" s="16"/>
     </row>
     <row r="164">
-      <c r="E164" s="17"/>
+      <c r="E164" s="16"/>
     </row>
     <row r="165">
-      <c r="E165" s="17"/>
+      <c r="E165" s="16"/>
     </row>
     <row r="166">
-      <c r="E166" s="17"/>
+      <c r="E166" s="16"/>
     </row>
     <row r="167">
-      <c r="E167" s="17"/>
+      <c r="E167" s="16"/>
     </row>
     <row r="168">
-      <c r="E168" s="17"/>
+      <c r="E168" s="16"/>
     </row>
     <row r="169">
-      <c r="E169" s="17"/>
+      <c r="E169" s="16"/>
     </row>
     <row r="170">
-      <c r="E170" s="17"/>
+      <c r="E170" s="16"/>
     </row>
     <row r="171">
-      <c r="E171" s="17"/>
+      <c r="E171" s="16"/>
     </row>
     <row r="172">
-      <c r="E172" s="17"/>
+      <c r="E172" s="16"/>
     </row>
     <row r="173">
-      <c r="E173" s="17"/>
+      <c r="E173" s="16"/>
     </row>
     <row r="174">
-      <c r="E174" s="17"/>
+      <c r="E174" s="16"/>
     </row>
     <row r="175">
-      <c r="E175" s="17"/>
+      <c r="E175" s="16"/>
     </row>
     <row r="176">
-      <c r="E176" s="17"/>
+      <c r="E176" s="16"/>
     </row>
     <row r="177">
-      <c r="E177" s="17"/>
+      <c r="E177" s="16"/>
     </row>
     <row r="178">
-      <c r="E178" s="17"/>
+      <c r="E178" s="16"/>
     </row>
     <row r="179">
-      <c r="E179" s="17"/>
+      <c r="E179" s="16"/>
     </row>
     <row r="180">
-      <c r="E180" s="17"/>
+      <c r="E180" s="16"/>
     </row>
     <row r="181">
-      <c r="E181" s="17"/>
+      <c r="E181" s="16"/>
     </row>
     <row r="182">
-      <c r="E182" s="17"/>
+      <c r="E182" s="16"/>
     </row>
     <row r="183">
-      <c r="E183" s="17"/>
+      <c r="E183" s="16"/>
     </row>
     <row r="184">
-      <c r="E184" s="17"/>
+      <c r="E184" s="16"/>
     </row>
     <row r="185">
-      <c r="E185" s="17"/>
+      <c r="E185" s="16"/>
     </row>
     <row r="186">
-      <c r="E186" s="17"/>
+      <c r="E186" s="16"/>
     </row>
     <row r="187">
-      <c r="E187" s="17"/>
+      <c r="E187" s="16"/>
     </row>
     <row r="188">
-      <c r="E188" s="17"/>
+      <c r="E188" s="16"/>
     </row>
     <row r="189">
-      <c r="E189" s="17"/>
+      <c r="E189" s="16"/>
     </row>
     <row r="190">
-      <c r="E190" s="17"/>
+      <c r="E190" s="16"/>
     </row>
     <row r="191">
-      <c r="E191" s="17"/>
+      <c r="E191" s="16"/>
     </row>
     <row r="192">
-      <c r="E192" s="17"/>
+      <c r="E192" s="16"/>
     </row>
     <row r="193">
-      <c r="E193" s="17"/>
+      <c r="E193" s="16"/>
     </row>
     <row r="194">
-      <c r="E194" s="17"/>
+      <c r="E194" s="16"/>
     </row>
     <row r="195">
-      <c r="E195" s="17"/>
+      <c r="E195" s="16"/>
     </row>
     <row r="196">
-      <c r="E196" s="17"/>
+      <c r="E196" s="16"/>
     </row>
     <row r="197">
-      <c r="E197" s="17"/>
+      <c r="E197" s="16"/>
     </row>
     <row r="198">
-      <c r="E198" s="17"/>
+      <c r="E198" s="16"/>
     </row>
     <row r="199">
-      <c r="E199" s="17"/>
+      <c r="E199" s="16"/>
     </row>
     <row r="200">
-      <c r="E200" s="17"/>
+      <c r="E200" s="16"/>
     </row>
     <row r="201">
-      <c r="E201" s="17"/>
+      <c r="E201" s="16"/>
     </row>
     <row r="202">
-      <c r="E202" s="17"/>
+      <c r="E202" s="16"/>
     </row>
     <row r="203">
-      <c r="E203" s="17"/>
+      <c r="E203" s="16"/>
     </row>
     <row r="204">
-      <c r="E204" s="17"/>
+      <c r="E204" s="16"/>
     </row>
     <row r="205">
-      <c r="E205" s="17"/>
+      <c r="E205" s="16"/>
     </row>
     <row r="206">
-      <c r="E206" s="17"/>
+      <c r="E206" s="16"/>
     </row>
     <row r="207">
-      <c r="E207" s="17"/>
+      <c r="E207" s="16"/>
     </row>
     <row r="208">
-      <c r="E208" s="17"/>
+      <c r="E208" s="16"/>
     </row>
     <row r="209">
-      <c r="E209" s="17"/>
+      <c r="E209" s="16"/>
     </row>
     <row r="210">
-      <c r="E210" s="17"/>
+      <c r="E210" s="16"/>
     </row>
     <row r="211">
-      <c r="E211" s="17"/>
+      <c r="E211" s="16"/>
     </row>
     <row r="212">
-      <c r="E212" s="17"/>
+      <c r="E212" s="16"/>
     </row>
     <row r="213">
-      <c r="E213" s="17"/>
+      <c r="E213" s="16"/>
     </row>
     <row r="214">
-      <c r="E214" s="17"/>
+      <c r="E214" s="16"/>
     </row>
     <row r="215">
-      <c r="E215" s="17"/>
+      <c r="E215" s="16"/>
     </row>
     <row r="216">
-      <c r="E216" s="17"/>
+      <c r="E216" s="16"/>
     </row>
     <row r="217">
-      <c r="E217" s="17"/>
+      <c r="E217" s="16"/>
     </row>
     <row r="218">
-      <c r="E218" s="17"/>
+      <c r="E218" s="16"/>
     </row>
     <row r="219">
-      <c r="E219" s="17"/>
+      <c r="E219" s="16"/>
     </row>
     <row r="220">
-      <c r="E220" s="17"/>
+      <c r="E220" s="16"/>
     </row>
     <row r="221">
-      <c r="E221" s="17"/>
+      <c r="E221" s="16"/>
     </row>
     <row r="222">
-      <c r="E222" s="17"/>
+      <c r="E222" s="16"/>
     </row>
     <row r="223">
-      <c r="E223" s="17"/>
+      <c r="E223" s="16"/>
     </row>
     <row r="224">
-      <c r="E224" s="17"/>
+      <c r="E224" s="16"/>
     </row>
     <row r="225">
-      <c r="E225" s="17"/>
+      <c r="E225" s="16"/>
     </row>
     <row r="226">
-      <c r="E226" s="17"/>
+      <c r="E226" s="16"/>
     </row>
     <row r="227">
-      <c r="E227" s="17"/>
+      <c r="E227" s="16"/>
     </row>
     <row r="228">
-      <c r="E228" s="17"/>
+      <c r="E228" s="16"/>
     </row>
     <row r="229">
-      <c r="E229" s="17"/>
+      <c r="E229" s="16"/>
     </row>
     <row r="230">
-      <c r="E230" s="17"/>
+      <c r="E230" s="16"/>
     </row>
     <row r="231">
-      <c r="E231" s="17"/>
+      <c r="E231" s="16"/>
     </row>
     <row r="232">
-      <c r="E232" s="17"/>
+      <c r="E232" s="16"/>
     </row>
     <row r="233">
-      <c r="E233" s="17"/>
+      <c r="E233" s="16"/>
     </row>
     <row r="234">
-      <c r="E234" s="17"/>
+      <c r="E234" s="16"/>
     </row>
     <row r="235">
-      <c r="E235" s="17"/>
+      <c r="E235" s="16"/>
     </row>
     <row r="236">
-      <c r="E236" s="17"/>
+      <c r="E236" s="16"/>
     </row>
     <row r="237">
-      <c r="E237" s="17"/>
+      <c r="E237" s="16"/>
     </row>
     <row r="238">
-      <c r="E238" s="17"/>
+      <c r="E238" s="16"/>
     </row>
     <row r="239">
-      <c r="E239" s="17"/>
+      <c r="E239" s="16"/>
     </row>
     <row r="240">
-      <c r="E240" s="17"/>
+      <c r="E240" s="16"/>
     </row>
     <row r="241">
-      <c r="E241" s="17"/>
+      <c r="E241" s="16"/>
     </row>
     <row r="242">
-      <c r="E242" s="17"/>
+      <c r="E242" s="16"/>
     </row>
     <row r="243">
-      <c r="E243" s="17"/>
+      <c r="E243" s="16"/>
     </row>
     <row r="244">
-      <c r="E244" s="17"/>
+      <c r="E244" s="16"/>
     </row>
     <row r="245">
-      <c r="E245" s="17"/>
+      <c r="E245" s="16"/>
     </row>
     <row r="246">
-      <c r="E246" s="17"/>
+      <c r="E246" s="16"/>
     </row>
     <row r="247">
-      <c r="E247" s="17"/>
+      <c r="E247" s="16"/>
     </row>
     <row r="248">
-      <c r="E248" s="17"/>
+      <c r="E248" s="16"/>
     </row>
     <row r="249">
-      <c r="E249" s="17"/>
+      <c r="E249" s="16"/>
     </row>
     <row r="250">
-      <c r="E250" s="17"/>
+      <c r="E250" s="16"/>
     </row>
     <row r="251">
-      <c r="E251" s="17"/>
+      <c r="E251" s="16"/>
     </row>
     <row r="252">
-      <c r="E252" s="17"/>
+      <c r="E252" s="16"/>
     </row>
     <row r="253">
-      <c r="E253" s="17"/>
+      <c r="E253" s="16"/>
     </row>
     <row r="254">
-      <c r="E254" s="17"/>
+      <c r="E254" s="16"/>
     </row>
     <row r="255">
-      <c r="E255" s="17"/>
+      <c r="E255" s="16"/>
     </row>
     <row r="256">
-      <c r="E256" s="17"/>
+      <c r="E256" s="16"/>
     </row>
     <row r="257">
-      <c r="E257" s="17"/>
+      <c r="E257" s="16"/>
     </row>
     <row r="258">
-      <c r="E258" s="17"/>
+      <c r="E258" s="16"/>
     </row>
     <row r="259">
-      <c r="E259" s="17"/>
+      <c r="E259" s="16"/>
     </row>
     <row r="260">
-      <c r="E260" s="17"/>
+      <c r="E260" s="16"/>
     </row>
     <row r="261">
-      <c r="E261" s="17"/>
+      <c r="E261" s="16"/>
     </row>
     <row r="262">
-      <c r="E262" s="17"/>
+      <c r="E262" s="16"/>
     </row>
     <row r="263">
-      <c r="E263" s="17"/>
+      <c r="E263" s="16"/>
     </row>
     <row r="264">
-      <c r="E264" s="17"/>
+      <c r="E264" s="16"/>
     </row>
     <row r="265">
-      <c r="E265" s="17"/>
+      <c r="E265" s="16"/>
     </row>
     <row r="266">
-      <c r="E266" s="17"/>
+      <c r="E266" s="16"/>
     </row>
     <row r="267">
-      <c r="E267" s="17"/>
+      <c r="E267" s="16"/>
     </row>
     <row r="268">
-      <c r="E268" s="17"/>
+      <c r="E268" s="16"/>
     </row>
     <row r="269">
-      <c r="E269" s="17"/>
+      <c r="E269" s="16"/>
     </row>
     <row r="270">
-      <c r="E270" s="17"/>
+      <c r="E270" s="16"/>
     </row>
     <row r="271">
-      <c r="E271" s="17"/>
+      <c r="E271" s="16"/>
     </row>
     <row r="272">
-      <c r="E272" s="17"/>
+      <c r="E272" s="16"/>
     </row>
     <row r="273">
-      <c r="E273" s="17"/>
+      <c r="E273" s="16"/>
     </row>
     <row r="274">
-      <c r="E274" s="17"/>
+      <c r="E274" s="16"/>
     </row>
     <row r="275">
-      <c r="E275" s="17"/>
+      <c r="E275" s="16"/>
     </row>
     <row r="276">
-      <c r="E276" s="17"/>
+      <c r="E276" s="16"/>
     </row>
     <row r="277">
-      <c r="E277" s="17"/>
+      <c r="E277" s="16"/>
     </row>
     <row r="278">
-      <c r="E278" s="17"/>
+      <c r="E278" s="16"/>
     </row>
     <row r="279">
-      <c r="E279" s="17"/>
+      <c r="E279" s="16"/>
     </row>
     <row r="280">
-      <c r="E280" s="17"/>
+      <c r="E280" s="16"/>
     </row>
     <row r="281">
-      <c r="E281" s="17"/>
+      <c r="E281" s="16"/>
     </row>
     <row r="282">
-      <c r="E282" s="17"/>
+      <c r="E282" s="16"/>
     </row>
     <row r="283">
-      <c r="E283" s="17"/>
+      <c r="E283" s="16"/>
     </row>
     <row r="284">
-      <c r="E284" s="17"/>
+      <c r="E284" s="16"/>
     </row>
     <row r="285">
-      <c r="E285" s="17"/>
+      <c r="E285" s="16"/>
     </row>
     <row r="286">
-      <c r="E286" s="17"/>
+      <c r="E286" s="16"/>
     </row>
     <row r="287">
-      <c r="E287" s="17"/>
+      <c r="E287" s="16"/>
     </row>
     <row r="288">
-      <c r="E288" s="17"/>
+      <c r="E288" s="16"/>
     </row>
     <row r="289">
-      <c r="E289" s="17"/>
+      <c r="E289" s="16"/>
     </row>
     <row r="290">
-      <c r="E290" s="17"/>
+      <c r="E290" s="16"/>
     </row>
     <row r="291">
-      <c r="E291" s="17"/>
+      <c r="E291" s="16"/>
     </row>
     <row r="292">
-      <c r="E292" s="17"/>
+      <c r="E292" s="16"/>
     </row>
     <row r="293">
-      <c r="E293" s="17"/>
+      <c r="E293" s="16"/>
     </row>
     <row r="294">
-      <c r="E294" s="17"/>
+      <c r="E294" s="16"/>
     </row>
     <row r="295">
-      <c r="E295" s="17"/>
+      <c r="E295" s="16"/>
     </row>
     <row r="296">
-      <c r="E296" s="17"/>
+      <c r="E296" s="16"/>
     </row>
     <row r="297">
-      <c r="E297" s="17"/>
+      <c r="E297" s="16"/>
     </row>
     <row r="298">
-      <c r="E298" s="17"/>
+      <c r="E298" s="16"/>
     </row>
     <row r="299">
-      <c r="E299" s="17"/>
+      <c r="E299" s="16"/>
     </row>
     <row r="300">
-      <c r="E300" s="17"/>
+      <c r="E300" s="16"/>
     </row>
     <row r="301">
-      <c r="E301" s="17"/>
+      <c r="E301" s="16"/>
     </row>
     <row r="302">
-      <c r="E302" s="17"/>
+      <c r="E302" s="16"/>
     </row>
     <row r="303">
-      <c r="E303" s="17"/>
+      <c r="E303" s="16"/>
     </row>
     <row r="304">
-      <c r="E304" s="17"/>
+      <c r="E304" s="16"/>
     </row>
     <row r="305">
-      <c r="E305" s="17"/>
+      <c r="E305" s="16"/>
     </row>
     <row r="306">
-      <c r="E306" s="17"/>
+      <c r="E306" s="16"/>
     </row>
     <row r="307">
-      <c r="E307" s="17"/>
+      <c r="E307" s="16"/>
     </row>
     <row r="308">
-      <c r="E308" s="17"/>
+      <c r="E308" s="16"/>
     </row>
     <row r="309">
-      <c r="E309" s="17"/>
+      <c r="E309" s="16"/>
     </row>
     <row r="310">
-      <c r="E310" s="17"/>
+      <c r="E310" s="16"/>
     </row>
     <row r="311">
-      <c r="E311" s="17"/>
+      <c r="E311" s="16"/>
     </row>
     <row r="312">
-      <c r="E312" s="17"/>
+      <c r="E312" s="16"/>
     </row>
     <row r="313">
-      <c r="E313" s="17"/>
+      <c r="E313" s="16"/>
     </row>
     <row r="314">
-      <c r="E314" s="17"/>
+      <c r="E314" s="16"/>
     </row>
     <row r="315">
-      <c r="E315" s="17"/>
+      <c r="E315" s="16"/>
     </row>
     <row r="316">
-      <c r="E316" s="17"/>
+      <c r="E316" s="16"/>
     </row>
     <row r="317">
-      <c r="E317" s="17"/>
+      <c r="E317" s="16"/>
     </row>
     <row r="318">
-      <c r="E318" s="17"/>
+      <c r="E318" s="16"/>
     </row>
     <row r="319">
-      <c r="E319" s="17"/>
+      <c r="E319" s="16"/>
     </row>
     <row r="320">
-      <c r="E320" s="17"/>
+      <c r="E320" s="16"/>
     </row>
     <row r="321">
-      <c r="E321" s="17"/>
+      <c r="E321" s="16"/>
     </row>
     <row r="322">
-      <c r="E322" s="17"/>
+      <c r="E322" s="16"/>
     </row>
     <row r="323">
-      <c r="E323" s="17"/>
+      <c r="E323" s="16"/>
     </row>
     <row r="324">
-      <c r="E324" s="17"/>
+      <c r="E324" s="16"/>
     </row>
     <row r="325">
-      <c r="E325" s="17"/>
+      <c r="E325" s="16"/>
     </row>
     <row r="326">
-      <c r="E326" s="17"/>
+      <c r="E326" s="16"/>
     </row>
     <row r="327">
-      <c r="E327" s="17"/>
+      <c r="E327" s="16"/>
     </row>
     <row r="328">
-      <c r="E328" s="17"/>
+      <c r="E328" s="16"/>
     </row>
     <row r="329">
-      <c r="E329" s="17"/>
+      <c r="E329" s="16"/>
     </row>
     <row r="330">
-      <c r="E330" s="17"/>
+      <c r="E330" s="16"/>
     </row>
     <row r="331">
-      <c r="E331" s="17"/>
+      <c r="E331" s="16"/>
     </row>
     <row r="332">
-      <c r="E332" s="17"/>
+      <c r="E332" s="16"/>
     </row>
     <row r="333">
-      <c r="E333" s="17"/>
+      <c r="E333" s="16"/>
     </row>
     <row r="334">
-      <c r="E334" s="17"/>
+      <c r="E334" s="16"/>
     </row>
     <row r="335">
-      <c r="E335" s="17"/>
+      <c r="E335" s="16"/>
     </row>
     <row r="336">
-      <c r="E336" s="17"/>
+      <c r="E336" s="16"/>
     </row>
     <row r="337">
-      <c r="E337" s="17"/>
+      <c r="E337" s="16"/>
     </row>
     <row r="338">
-      <c r="E338" s="17"/>
+      <c r="E338" s="16"/>
     </row>
     <row r="339">
-      <c r="E339" s="17"/>
+      <c r="E339" s="16"/>
     </row>
     <row r="340">
-      <c r="E340" s="17"/>
+      <c r="E340" s="16"/>
     </row>
     <row r="341">
-      <c r="E341" s="17"/>
+      <c r="E341" s="16"/>
     </row>
     <row r="342">
-      <c r="E342" s="17"/>
+      <c r="E342" s="16"/>
     </row>
     <row r="343">
-      <c r="E343" s="17"/>
+      <c r="E343" s="16"/>
     </row>
     <row r="344">
-      <c r="E344" s="17"/>
+      <c r="E344" s="16"/>
     </row>
     <row r="345">
-      <c r="E345" s="17"/>
+      <c r="E345" s="16"/>
     </row>
     <row r="346">
-      <c r="E346" s="17"/>
+      <c r="E346" s="16"/>
     </row>
     <row r="347">
-      <c r="E347" s="17"/>
+      <c r="E347" s="16"/>
     </row>
     <row r="348">
-      <c r="E348" s="17"/>
+      <c r="E348" s="16"/>
     </row>
     <row r="349">
-      <c r="E349" s="17"/>
+      <c r="E349" s="16"/>
     </row>
     <row r="350">
-      <c r="E350" s="17"/>
+      <c r="E350" s="16"/>
     </row>
     <row r="351">
-      <c r="E351" s="17"/>
+      <c r="E351" s="16"/>
     </row>
     <row r="352">
-      <c r="E352" s="17"/>
+      <c r="E352" s="16"/>
     </row>
     <row r="353">
-      <c r="E353" s="17"/>
+      <c r="E353" s="16"/>
     </row>
     <row r="354">
-      <c r="E354" s="17"/>
+      <c r="E354" s="16"/>
     </row>
     <row r="355">
-      <c r="E355" s="17"/>
+      <c r="E355" s="16"/>
     </row>
     <row r="356">
-      <c r="E356" s="17"/>
+      <c r="E356" s="16"/>
     </row>
     <row r="357">
-      <c r="E357" s="17"/>
+      <c r="E357" s="16"/>
     </row>
     <row r="358">
-      <c r="E358" s="17"/>
+      <c r="E358" s="16"/>
     </row>
     <row r="359">
-      <c r="E359" s="17"/>
+      <c r="E359" s="16"/>
     </row>
     <row r="360">
-      <c r="E360" s="17"/>
+      <c r="E360" s="16"/>
     </row>
     <row r="361">
-      <c r="E361" s="17"/>
+      <c r="E361" s="16"/>
     </row>
     <row r="362">
-      <c r="E362" s="17"/>
+      <c r="E362" s="16"/>
     </row>
     <row r="363">
-      <c r="E363" s="17"/>
+      <c r="E363" s="16"/>
     </row>
     <row r="364">
-      <c r="E364" s="17"/>
+      <c r="E364" s="16"/>
     </row>
     <row r="365">
-      <c r="E365" s="17"/>
+      <c r="E365" s="16"/>
     </row>
     <row r="366">
-      <c r="E366" s="17"/>
+      <c r="E366" s="16"/>
     </row>
     <row r="367">
-      <c r="E367" s="17"/>
+      <c r="E367" s="16"/>
     </row>
     <row r="368">
-      <c r="E368" s="17"/>
+      <c r="E368" s="16"/>
     </row>
     <row r="369">
-      <c r="E369" s="17"/>
+      <c r="E369" s="16"/>
     </row>
     <row r="370">
-      <c r="E370" s="17"/>
+      <c r="E370" s="16"/>
     </row>
     <row r="371">
-      <c r="E371" s="17"/>
+      <c r="E371" s="16"/>
     </row>
     <row r="372">
-      <c r="E372" s="17"/>
+      <c r="E372" s="16"/>
     </row>
     <row r="373">
-      <c r="E373" s="17"/>
+      <c r="E373" s="16"/>
     </row>
     <row r="374">
-      <c r="E374" s="17"/>
+      <c r="E374" s="16"/>
     </row>
     <row r="375">
-      <c r="E375" s="17"/>
+      <c r="E375" s="16"/>
     </row>
     <row r="376">
-      <c r="E376" s="17"/>
+      <c r="E376" s="16"/>
     </row>
     <row r="377">
-      <c r="E377" s="17"/>
+      <c r="E377" s="16"/>
     </row>
     <row r="378">
-      <c r="E378" s="17"/>
+      <c r="E378" s="16"/>
     </row>
     <row r="379">
-      <c r="E379" s="17"/>
+      <c r="E379" s="16"/>
     </row>
     <row r="380">
-      <c r="E380" s="17"/>
+      <c r="E380" s="16"/>
     </row>
     <row r="381">
-      <c r="E381" s="17"/>
+      <c r="E381" s="16"/>
     </row>
     <row r="382">
-      <c r="E382" s="17"/>
+      <c r="E382" s="16"/>
     </row>
     <row r="383">
-      <c r="E383" s="17"/>
+      <c r="E383" s="16"/>
     </row>
     <row r="384">
-      <c r="E384" s="17"/>
+      <c r="E384" s="16"/>
     </row>
     <row r="385">
-      <c r="E385" s="17"/>
+      <c r="E385" s="16"/>
     </row>
     <row r="386">
-      <c r="E386" s="17"/>
+      <c r="E386" s="16"/>
     </row>
     <row r="387">
-      <c r="E387" s="17"/>
+      <c r="E387" s="16"/>
     </row>
     <row r="388">
-      <c r="E388" s="17"/>
+      <c r="E388" s="16"/>
     </row>
     <row r="389">
-      <c r="E389" s="17"/>
+      <c r="E389" s="16"/>
     </row>
     <row r="390">
-      <c r="E390" s="17"/>
+      <c r="E390" s="16"/>
     </row>
     <row r="391">
-      <c r="E391" s="17"/>
+      <c r="E391" s="16"/>
     </row>
     <row r="392">
-      <c r="E392" s="17"/>
+      <c r="E392" s="16"/>
     </row>
     <row r="393">
-      <c r="E393" s="17"/>
+      <c r="E393" s="16"/>
     </row>
     <row r="394">
-      <c r="E394" s="17"/>
+      <c r="E394" s="16"/>
     </row>
     <row r="395">
-      <c r="E395" s="17"/>
+      <c r="E395" s="16"/>
     </row>
     <row r="396">
-      <c r="E396" s="17"/>
+      <c r="E396" s="16"/>
     </row>
     <row r="397">
-      <c r="E397" s="17"/>
+      <c r="E397" s="16"/>
     </row>
     <row r="398">
-      <c r="E398" s="17"/>
+      <c r="E398" s="16"/>
     </row>
     <row r="399">
-      <c r="E399" s="17"/>
+      <c r="E399" s="16"/>
     </row>
     <row r="400">
-      <c r="E400" s="17"/>
+      <c r="E400" s="16"/>
     </row>
     <row r="401">
-      <c r="E401" s="17"/>
+      <c r="E401" s="16"/>
     </row>
     <row r="402">
-      <c r="E402" s="17"/>
+      <c r="E402" s="16"/>
     </row>
     <row r="403">
-      <c r="E403" s="17"/>
+      <c r="E403" s="16"/>
     </row>
     <row r="404">
-      <c r="E404" s="17"/>
+      <c r="E404" s="16"/>
     </row>
     <row r="405">
-      <c r="E405" s="17"/>
+      <c r="E405" s="16"/>
     </row>
     <row r="406">
-      <c r="E406" s="17"/>
+      <c r="E406" s="16"/>
     </row>
     <row r="407">
-      <c r="E407" s="17"/>
+      <c r="E407" s="16"/>
     </row>
     <row r="408">
-      <c r="E408" s="17"/>
+      <c r="E408" s="16"/>
     </row>
     <row r="409">
-      <c r="E409" s="17"/>
+      <c r="E409" s="16"/>
     </row>
     <row r="410">
-      <c r="E410" s="17"/>
+      <c r="E410" s="16"/>
     </row>
     <row r="411">
-      <c r="E411" s="17"/>
+      <c r="E411" s="16"/>
     </row>
     <row r="412">
-      <c r="E412" s="17"/>
+      <c r="E412" s="16"/>
     </row>
     <row r="413">
-      <c r="E413" s="17"/>
+      <c r="E413" s="16"/>
     </row>
     <row r="414">
-      <c r="E414" s="17"/>
+      <c r="E414" s="16"/>
     </row>
     <row r="415">
-      <c r="E415" s="17"/>
+      <c r="E415" s="16"/>
     </row>
     <row r="416">
-      <c r="E416" s="17"/>
+      <c r="E416" s="16"/>
     </row>
     <row r="417">
-      <c r="E417" s="17"/>
+      <c r="E417" s="16"/>
     </row>
     <row r="418">
-      <c r="E418" s="17"/>
+      <c r="E418" s="16"/>
     </row>
     <row r="419">
-      <c r="E419" s="17"/>
+      <c r="E419" s="16"/>
     </row>
     <row r="420">
-      <c r="E420" s="17"/>
+      <c r="E420" s="16"/>
     </row>
     <row r="421">
-      <c r="E421" s="17"/>
+      <c r="E421" s="16"/>
     </row>
     <row r="422">
-      <c r="E422" s="17"/>
+      <c r="E422" s="16"/>
     </row>
     <row r="423">
-      <c r="E423" s="17"/>
+      <c r="E423" s="16"/>
     </row>
     <row r="424">
-      <c r="E424" s="17"/>
+      <c r="E424" s="16"/>
     </row>
     <row r="425">
-      <c r="E425" s="17"/>
+      <c r="E425" s="16"/>
     </row>
     <row r="426">
-      <c r="E426" s="17"/>
+      <c r="E426" s="16"/>
     </row>
     <row r="427">
-      <c r="E427" s="17"/>
+      <c r="E427" s="16"/>
     </row>
     <row r="428">
-      <c r="E428" s="17"/>
+      <c r="E428" s="16"/>
     </row>
     <row r="429">
-      <c r="E429" s="17"/>
+      <c r="E429" s="16"/>
     </row>
     <row r="430">
-      <c r="E430" s="17"/>
+      <c r="E430" s="16"/>
     </row>
     <row r="431">
-      <c r="E431" s="17"/>
+      <c r="E431" s="16"/>
     </row>
     <row r="432">
-      <c r="E432" s="17"/>
+      <c r="E432" s="16"/>
     </row>
     <row r="433">
-      <c r="E433" s="17"/>
+      <c r="E433" s="16"/>
     </row>
     <row r="434">
-      <c r="E434" s="17"/>
+      <c r="E434" s="16"/>
     </row>
     <row r="435">
-      <c r="E435" s="17"/>
+      <c r="E435" s="16"/>
     </row>
     <row r="436">
-      <c r="E436" s="17"/>
+      <c r="E436" s="16"/>
     </row>
     <row r="437">
-      <c r="E437" s="17"/>
+      <c r="E437" s="16"/>
     </row>
     <row r="438">
-      <c r="E438" s="17"/>
+      <c r="E438" s="16"/>
     </row>
     <row r="439">
-      <c r="E439" s="17"/>
+      <c r="E439" s="16"/>
     </row>
     <row r="440">
-      <c r="E440" s="17"/>
+      <c r="E440" s="16"/>
     </row>
     <row r="441">
-      <c r="E441" s="17"/>
+      <c r="E441" s="16"/>
     </row>
     <row r="442">
-      <c r="E442" s="17"/>
+      <c r="E442" s="16"/>
     </row>
     <row r="443">
-      <c r="E443" s="17"/>
+      <c r="E443" s="16"/>
     </row>
     <row r="444">
-      <c r="E444" s="17"/>
+      <c r="E444" s="16"/>
     </row>
     <row r="445">
-      <c r="E445" s="17"/>
+      <c r="E445" s="16"/>
     </row>
     <row r="446">
-      <c r="E446" s="17"/>
+      <c r="E446" s="16"/>
     </row>
     <row r="447">
-      <c r="E447" s="17"/>
+      <c r="E447" s="16"/>
     </row>
     <row r="448">
-      <c r="E448" s="17"/>
+      <c r="E448" s="16"/>
     </row>
     <row r="449">
-      <c r="E449" s="17"/>
+      <c r="E449" s="16"/>
     </row>
     <row r="450">
-      <c r="E450" s="17"/>
+      <c r="E450" s="16"/>
     </row>
     <row r="451">
-      <c r="E451" s="17"/>
+      <c r="E451" s="16"/>
     </row>
     <row r="452">
-      <c r="E452" s="17"/>
+      <c r="E452" s="16"/>
     </row>
     <row r="453">
-      <c r="E453" s="17"/>
+      <c r="E453" s="16"/>
     </row>
     <row r="454">
-      <c r="E454" s="17"/>
+      <c r="E454" s="16"/>
     </row>
     <row r="455">
-      <c r="E455" s="17"/>
+      <c r="E455" s="16"/>
     </row>
     <row r="456">
-      <c r="E456" s="17"/>
+      <c r="E456" s="16"/>
     </row>
     <row r="457">
-      <c r="E457" s="17"/>
+      <c r="E457" s="16"/>
     </row>
     <row r="458">
-      <c r="E458" s="17"/>
+      <c r="E458" s="16"/>
     </row>
     <row r="459">
-      <c r="E459" s="17"/>
+      <c r="E459" s="16"/>
     </row>
     <row r="460">
-      <c r="E460" s="17"/>
+      <c r="E460" s="16"/>
     </row>
     <row r="461">
-      <c r="E461" s="17"/>
+      <c r="E461" s="16"/>
     </row>
     <row r="462">
-      <c r="E462" s="17"/>
+      <c r="E462" s="16"/>
     </row>
     <row r="463">
-      <c r="E463" s="17"/>
+      <c r="E463" s="16"/>
     </row>
     <row r="464">
-      <c r="E464" s="17"/>
+      <c r="E464" s="16"/>
     </row>
     <row r="465">
-      <c r="E465" s="17"/>
+      <c r="E465" s="16"/>
     </row>
     <row r="466">
-      <c r="E466" s="17"/>
+      <c r="E466" s="16"/>
     </row>
     <row r="467">
-      <c r="E467" s="17"/>
+      <c r="E467" s="16"/>
     </row>
     <row r="468">
-      <c r="E468" s="17"/>
+      <c r="E468" s="16"/>
     </row>
     <row r="469">
-      <c r="E469" s="17"/>
+      <c r="E469" s="16"/>
     </row>
     <row r="470">
-      <c r="E470" s="17"/>
+      <c r="E470" s="16"/>
     </row>
     <row r="471">
-      <c r="E471" s="17"/>
+      <c r="E471" s="16"/>
     </row>
     <row r="472">
-      <c r="E472" s="17"/>
+      <c r="E472" s="16"/>
     </row>
     <row r="473">
-      <c r="E473" s="17"/>
+      <c r="E473" s="16"/>
     </row>
     <row r="474">
-      <c r="E474" s="17"/>
+      <c r="E474" s="16"/>
     </row>
     <row r="475">
-      <c r="E475" s="17"/>
+      <c r="E475" s="16"/>
     </row>
     <row r="476">
-      <c r="E476" s="17"/>
+      <c r="E476" s="16"/>
     </row>
     <row r="477">
-      <c r="E477" s="17"/>
+      <c r="E477" s="16"/>
     </row>
     <row r="478">
-      <c r="E478" s="17"/>
+      <c r="E478" s="16"/>
     </row>
     <row r="479">
-      <c r="E479" s="17"/>
+      <c r="E479" s="16"/>
     </row>
     <row r="480">
-      <c r="E480" s="17"/>
+      <c r="E480" s="16"/>
     </row>
     <row r="481">
-      <c r="E481" s="17"/>
+      <c r="E481" s="16"/>
     </row>
     <row r="482">
-      <c r="E482" s="17"/>
+      <c r="E482" s="16"/>
     </row>
     <row r="483">
-      <c r="E483" s="17"/>
+      <c r="E483" s="16"/>
     </row>
     <row r="484">
-      <c r="E484" s="17"/>
+      <c r="E484" s="16"/>
     </row>
     <row r="485">
-      <c r="E485" s="17"/>
+      <c r="E485" s="16"/>
     </row>
     <row r="486">
-      <c r="E486" s="17"/>
+      <c r="E486" s="16"/>
     </row>
     <row r="487">
-      <c r="E487" s="17"/>
+      <c r="E487" s="16"/>
     </row>
     <row r="488">
-      <c r="E488" s="17"/>
+      <c r="E488" s="16"/>
     </row>
     <row r="489">
-      <c r="E489" s="17"/>
+      <c r="E489" s="16"/>
     </row>
     <row r="490">
-      <c r="E490" s="17"/>
+      <c r="E490" s="16"/>
     </row>
     <row r="491">
-      <c r="E491" s="17"/>
+      <c r="E491" s="16"/>
     </row>
     <row r="492">
-      <c r="E492" s="17"/>
+      <c r="E492" s="16"/>
     </row>
     <row r="493">
-      <c r="E493" s="17"/>
+      <c r="E493" s="16"/>
     </row>
     <row r="494">
-      <c r="E494" s="17"/>
+      <c r="E494" s="16"/>
     </row>
     <row r="495">
-      <c r="E495" s="17"/>
+      <c r="E495" s="16"/>
     </row>
     <row r="496">
-      <c r="E496" s="17"/>
+      <c r="E496" s="16"/>
     </row>
     <row r="497">
-      <c r="E497" s="17"/>
+      <c r="E497" s="16"/>
     </row>
     <row r="498">
-      <c r="E498" s="17"/>
+      <c r="E498" s="16"/>
     </row>
     <row r="499">
-      <c r="E499" s="17"/>
+      <c r="E499" s="16"/>
     </row>
     <row r="500">
-      <c r="E500" s="17"/>
+      <c r="E500" s="16"/>
     </row>
     <row r="501">
-      <c r="E501" s="17"/>
+      <c r="E501" s="16"/>
     </row>
     <row r="502">
-      <c r="E502" s="17"/>
+      <c r="E502" s="16"/>
     </row>
     <row r="503">
-      <c r="E503" s="17"/>
+      <c r="E503" s="16"/>
     </row>
     <row r="504">
-      <c r="E504" s="17"/>
+      <c r="E504" s="16"/>
     </row>
     <row r="505">
-      <c r="E505" s="17"/>
+      <c r="E505" s="16"/>
     </row>
     <row r="506">
-      <c r="E506" s="17"/>
+      <c r="E506" s="16"/>
     </row>
     <row r="507">
-      <c r="E507" s="17"/>
+      <c r="E507" s="16"/>
     </row>
     <row r="508">
-      <c r="E508" s="17"/>
+      <c r="E508" s="16"/>
     </row>
     <row r="509">
-      <c r="E509" s="17"/>
+      <c r="E509" s="16"/>
     </row>
     <row r="510">
-      <c r="E510" s="17"/>
+      <c r="E510" s="16"/>
     </row>
     <row r="511">
-      <c r="E511" s="17"/>
+      <c r="E511" s="16"/>
     </row>
     <row r="512">
-      <c r="E512" s="17"/>
+      <c r="E512" s="16"/>
     </row>
     <row r="513">
-      <c r="E513" s="17"/>
+      <c r="E513" s="16"/>
     </row>
     <row r="514">
-      <c r="E514" s="17"/>
+      <c r="E514" s="16"/>
     </row>
     <row r="515">
-      <c r="E515" s="17"/>
+      <c r="E515" s="16"/>
     </row>
     <row r="516">
-      <c r="E516" s="17"/>
+      <c r="E516" s="16"/>
     </row>
     <row r="517">
-      <c r="E517" s="17"/>
+      <c r="E517" s="16"/>
     </row>
     <row r="518">
-      <c r="E518" s="17"/>
+      <c r="E518" s="16"/>
     </row>
     <row r="519">
-      <c r="E519" s="17"/>
+      <c r="E519" s="16"/>
     </row>
     <row r="520">
-      <c r="E520" s="17"/>
+      <c r="E520" s="16"/>
     </row>
     <row r="521">
-      <c r="E521" s="17"/>
+      <c r="E521" s="16"/>
     </row>
     <row r="522">
-      <c r="E522" s="17"/>
+      <c r="E522" s="16"/>
     </row>
     <row r="523">
-      <c r="E523" s="17"/>
+      <c r="E523" s="16"/>
     </row>
     <row r="524">
-      <c r="E524" s="17"/>
+      <c r="E524" s="16"/>
     </row>
     <row r="525">
-      <c r="E525" s="17"/>
+      <c r="E525" s="16"/>
     </row>
     <row r="526">
-      <c r="E526" s="17"/>
+      <c r="E526" s="16"/>
     </row>
     <row r="527">
-      <c r="E527" s="17"/>
+      <c r="E527" s="16"/>
     </row>
     <row r="528">
-      <c r="E528" s="17"/>
+      <c r="E528" s="16"/>
     </row>
     <row r="529">
-      <c r="E529" s="17"/>
+      <c r="E529" s="16"/>
     </row>
     <row r="530">
-      <c r="E530" s="17"/>
+      <c r="E530" s="16"/>
     </row>
     <row r="531">
-      <c r="E531" s="17"/>
+      <c r="E531" s="16"/>
     </row>
     <row r="532">
-      <c r="E532" s="17"/>
+      <c r="E532" s="16"/>
     </row>
     <row r="533">
-      <c r="E533" s="17"/>
+      <c r="E533" s="16"/>
     </row>
     <row r="534">
-      <c r="E534" s="17"/>
+      <c r="E534" s="16"/>
     </row>
     <row r="535">
-      <c r="E535" s="17"/>
+      <c r="E535" s="16"/>
     </row>
     <row r="536">
-      <c r="E536" s="17"/>
+      <c r="E536" s="16"/>
     </row>
     <row r="537">
-      <c r="E537" s="17"/>
+      <c r="E537" s="16"/>
     </row>
     <row r="538">
-      <c r="E538" s="17"/>
+      <c r="E538" s="16"/>
     </row>
     <row r="539">
-      <c r="E539" s="17"/>
+      <c r="E539" s="16"/>
     </row>
     <row r="540">
-      <c r="E540" s="17"/>
+      <c r="E540" s="16"/>
     </row>
     <row r="541">
-      <c r="E541" s="17"/>
+      <c r="E541" s="16"/>
     </row>
     <row r="542">
-      <c r="E542" s="17"/>
+      <c r="E542" s="16"/>
     </row>
     <row r="543">
-      <c r="E543" s="17"/>
+      <c r="E543" s="16"/>
     </row>
     <row r="544">
-      <c r="E544" s="17"/>
+      <c r="E544" s="16"/>
     </row>
     <row r="545">
-      <c r="E545" s="17"/>
+      <c r="E545" s="16"/>
     </row>
     <row r="546">
-      <c r="E546" s="17"/>
+      <c r="E546" s="16"/>
     </row>
     <row r="547">
-      <c r="E547" s="17"/>
+      <c r="E547" s="16"/>
     </row>
     <row r="548">
-      <c r="E548" s="17"/>
+      <c r="E548" s="16"/>
     </row>
     <row r="549">
-      <c r="E549" s="17"/>
+      <c r="E549" s="16"/>
     </row>
     <row r="550">
-      <c r="E550" s="17"/>
+      <c r="E550" s="16"/>
     </row>
     <row r="551">
-      <c r="E551" s="17"/>
+      <c r="E551" s="16"/>
     </row>
     <row r="552">
-      <c r="E552" s="17"/>
+      <c r="E552" s="16"/>
     </row>
     <row r="553">
-      <c r="E553" s="17"/>
+      <c r="E553" s="16"/>
     </row>
     <row r="554">
-      <c r="E554" s="17"/>
+      <c r="E554" s="16"/>
     </row>
     <row r="555">
-      <c r="E555" s="17"/>
+      <c r="E555" s="16"/>
     </row>
     <row r="556">
-      <c r="E556" s="17"/>
+      <c r="E556" s="16"/>
     </row>
     <row r="557">
-      <c r="E557" s="17"/>
+      <c r="E557" s="16"/>
     </row>
     <row r="558">
-      <c r="E558" s="17"/>
+      <c r="E558" s="16"/>
     </row>
     <row r="559">
-      <c r="E559" s="17"/>
+      <c r="E559" s="16"/>
     </row>
     <row r="560">
-      <c r="E560" s="17"/>
+      <c r="E560" s="16"/>
     </row>
     <row r="561">
-      <c r="E561" s="17"/>
+      <c r="E561" s="16"/>
     </row>
     <row r="562">
-      <c r="E562" s="17"/>
+      <c r="E562" s="16"/>
     </row>
     <row r="563">
-      <c r="E563" s="17"/>
+      <c r="E563" s="16"/>
     </row>
     <row r="564">
-      <c r="E564" s="17"/>
+      <c r="E564" s="16"/>
     </row>
     <row r="565">
-      <c r="E565" s="17"/>
+      <c r="E565" s="16"/>
     </row>
     <row r="566">
-      <c r="E566" s="17"/>
+      <c r="E566" s="16"/>
     </row>
     <row r="567">
-      <c r="E567" s="17"/>
+      <c r="E567" s="16"/>
     </row>
     <row r="568">
-      <c r="E568" s="17"/>
+      <c r="E568" s="16"/>
     </row>
     <row r="569">
-      <c r="E569" s="17"/>
+      <c r="E569" s="16"/>
     </row>
     <row r="570">
-      <c r="E570" s="17"/>
+      <c r="E570" s="16"/>
     </row>
     <row r="571">
-      <c r="E571" s="17"/>
+      <c r="E571" s="16"/>
     </row>
     <row r="572">
-      <c r="E572" s="17"/>
+      <c r="E572" s="16"/>
     </row>
     <row r="573">
-      <c r="E573" s="17"/>
+      <c r="E573" s="16"/>
     </row>
     <row r="574">
-      <c r="E574" s="17"/>
+      <c r="E574" s="16"/>
     </row>
     <row r="575">
-      <c r="E575" s="17"/>
+      <c r="E575" s="16"/>
     </row>
     <row r="576">
-      <c r="E576" s="17"/>
+      <c r="E576" s="16"/>
     </row>
     <row r="577">
-      <c r="E577" s="17"/>
+      <c r="E577" s="16"/>
     </row>
     <row r="578">
-      <c r="E578" s="17"/>
+      <c r="E578" s="16"/>
     </row>
     <row r="579">
-      <c r="E579" s="17"/>
+      <c r="E579" s="16"/>
     </row>
     <row r="580">
-      <c r="E580" s="17"/>
+      <c r="E580" s="16"/>
     </row>
     <row r="581">
-      <c r="E581" s="17"/>
+      <c r="E581" s="16"/>
     </row>
     <row r="582">
-      <c r="E582" s="17"/>
+      <c r="E582" s="16"/>
     </row>
     <row r="583">
-      <c r="E583" s="17"/>
+      <c r="E583" s="16"/>
     </row>
     <row r="584">
-      <c r="E584" s="17"/>
+      <c r="E584" s="16"/>
     </row>
     <row r="585">
-      <c r="E585" s="17"/>
+      <c r="E585" s="16"/>
     </row>
     <row r="586">
-      <c r="E586" s="17"/>
+      <c r="E586" s="16"/>
     </row>
     <row r="587">
-      <c r="E587" s="17"/>
+      <c r="E587" s="16"/>
     </row>
     <row r="588">
-      <c r="E588" s="17"/>
+      <c r="E588" s="16"/>
     </row>
     <row r="589">
-      <c r="E589" s="17"/>
+      <c r="E589" s="16"/>
     </row>
     <row r="590">
-      <c r="E590" s="17"/>
+      <c r="E590" s="16"/>
     </row>
     <row r="591">
-      <c r="E591" s="17"/>
+      <c r="E591" s="16"/>
     </row>
     <row r="592">
-      <c r="E592" s="17"/>
+      <c r="E592" s="16"/>
     </row>
     <row r="593">
-      <c r="E593" s="17"/>
+      <c r="E593" s="16"/>
     </row>
     <row r="594">
-      <c r="E594" s="17"/>
+      <c r="E594" s="16"/>
     </row>
     <row r="595">
-      <c r="E595" s="17"/>
+      <c r="E595" s="16"/>
     </row>
     <row r="596">
-      <c r="E596" s="17"/>
+      <c r="E596" s="16"/>
     </row>
     <row r="597">
-      <c r="E597" s="17"/>
+      <c r="E597" s="16"/>
     </row>
     <row r="598">
-      <c r="E598" s="17"/>
+      <c r="E598" s="16"/>
     </row>
     <row r="599">
-      <c r="E599" s="17"/>
+      <c r="E599" s="16"/>
     </row>
     <row r="600">
-      <c r="E600" s="17"/>
+      <c r="E600" s="16"/>
     </row>
     <row r="601">
-      <c r="E601" s="17"/>
+      <c r="E601" s="16"/>
     </row>
     <row r="602">
-      <c r="E602" s="17"/>
+      <c r="E602" s="16"/>
     </row>
     <row r="603">
-      <c r="E603" s="17"/>
+      <c r="E603" s="16"/>
     </row>
     <row r="604">
-      <c r="E604" s="17"/>
+      <c r="E604" s="16"/>
     </row>
     <row r="605">
-      <c r="E605" s="17"/>
+      <c r="E605" s="16"/>
     </row>
     <row r="606">
-      <c r="E606" s="17"/>
+      <c r="E606" s="16"/>
     </row>
     <row r="607">
-      <c r="E607" s="17"/>
+      <c r="E607" s="16"/>
     </row>
     <row r="608">
-      <c r="E608" s="17"/>
+      <c r="E608" s="16"/>
     </row>
     <row r="609">
-      <c r="E609" s="17"/>
+      <c r="E609" s="16"/>
     </row>
     <row r="610">
-      <c r="E610" s="17"/>
+      <c r="E610" s="16"/>
     </row>
     <row r="611">
-      <c r="E611" s="17"/>
+      <c r="E611" s="16"/>
     </row>
     <row r="612">
-      <c r="E612" s="17"/>
+      <c r="E612" s="16"/>
     </row>
     <row r="613">
-      <c r="E613" s="17"/>
+      <c r="E613" s="16"/>
     </row>
     <row r="614">
-      <c r="E614" s="17"/>
+      <c r="E614" s="16"/>
     </row>
     <row r="615">
-      <c r="E615" s="17"/>
+      <c r="E615" s="16"/>
     </row>
     <row r="616">
-      <c r="E616" s="17"/>
+      <c r="E616" s="16"/>
     </row>
     <row r="617">
-      <c r="E617" s="17"/>
+      <c r="E617" s="16"/>
     </row>
     <row r="618">
-      <c r="E618" s="17"/>
+      <c r="E618" s="16"/>
     </row>
     <row r="619">
-      <c r="E619" s="17"/>
+      <c r="E619" s="16"/>
     </row>
     <row r="620">
-      <c r="E620" s="17"/>
+      <c r="E620" s="16"/>
     </row>
     <row r="621">
-      <c r="E621" s="17"/>
+      <c r="E621" s="16"/>
     </row>
     <row r="622">
-      <c r="E622" s="17"/>
+      <c r="E622" s="16"/>
     </row>
     <row r="623">
-      <c r="E623" s="17"/>
+      <c r="E623" s="16"/>
     </row>
     <row r="624">
-      <c r="E624" s="17"/>
+      <c r="E624" s="16"/>
     </row>
     <row r="625">
-      <c r="E625" s="17"/>
+      <c r="E625" s="16"/>
     </row>
     <row r="626">
-      <c r="E626" s="17"/>
+      <c r="E626" s="16"/>
     </row>
     <row r="627">
-      <c r="E627" s="17"/>
+      <c r="E627" s="16"/>
     </row>
     <row r="628">
-      <c r="E628" s="17"/>
+      <c r="E628" s="16"/>
     </row>
     <row r="629">
-      <c r="E629" s="17"/>
+      <c r="E629" s="16"/>
     </row>
     <row r="630">
-      <c r="E630" s="17"/>
+      <c r="E630" s="16"/>
     </row>
     <row r="631">
-      <c r="E631" s="17"/>
+      <c r="E631" s="16"/>
     </row>
     <row r="632">
-      <c r="E632" s="17"/>
+      <c r="E632" s="16"/>
     </row>
     <row r="633">
-      <c r="E633" s="17"/>
+      <c r="E633" s="16"/>
     </row>
     <row r="634">
-      <c r="E634" s="17"/>
+      <c r="E634" s="16"/>
     </row>
     <row r="635">
-      <c r="E635" s="17"/>
+      <c r="E635" s="16"/>
     </row>
     <row r="636">
-      <c r="E636" s="17"/>
+      <c r="E636" s="16"/>
     </row>
     <row r="637">
-      <c r="E637" s="17"/>
+      <c r="E637" s="16"/>
     </row>
     <row r="638">
-      <c r="E638" s="17"/>
+      <c r="E638" s="16"/>
     </row>
     <row r="639">
-      <c r="E639" s="17"/>
+      <c r="E639" s="16"/>
     </row>
     <row r="640">
-      <c r="E640" s="17"/>
+      <c r="E640" s="16"/>
     </row>
     <row r="641">
-      <c r="E641" s="17"/>
+      <c r="E641" s="16"/>
     </row>
     <row r="642">
-      <c r="E642" s="17"/>
+      <c r="E642" s="16"/>
     </row>
     <row r="643">
-      <c r="E643" s="17"/>
+      <c r="E643" s="16"/>
     </row>
     <row r="644">
-      <c r="E644" s="17"/>
+      <c r="E644" s="16"/>
     </row>
     <row r="645">
-      <c r="E645" s="17"/>
+      <c r="E645" s="16"/>
     </row>
     <row r="646">
-      <c r="E646" s="17"/>
+      <c r="E646" s="16"/>
     </row>
     <row r="647">
-      <c r="E647" s="17"/>
+      <c r="E647" s="16"/>
     </row>
     <row r="648">
-      <c r="E648" s="17"/>
+      <c r="E648" s="16"/>
     </row>
     <row r="649">
-      <c r="E649" s="17"/>
+      <c r="E649" s="16"/>
     </row>
     <row r="650">
-      <c r="E650" s="17"/>
+      <c r="E650" s="16"/>
     </row>
     <row r="651">
-      <c r="E651" s="17"/>
+      <c r="E651" s="16"/>
     </row>
     <row r="652">
-      <c r="E652" s="17"/>
+      <c r="E652" s="16"/>
     </row>
     <row r="653">
-      <c r="E653" s="17"/>
+      <c r="E653" s="16"/>
     </row>
     <row r="654">
-      <c r="E654" s="17"/>
+      <c r="E654" s="16"/>
     </row>
     <row r="655">
-      <c r="E655" s="17"/>
+      <c r="E655" s="16"/>
     </row>
     <row r="656">
-      <c r="E656" s="17"/>
+      <c r="E656" s="16"/>
     </row>
     <row r="657">
-      <c r="E657" s="17"/>
+      <c r="E657" s="16"/>
     </row>
     <row r="658">
-      <c r="E658" s="17"/>
+      <c r="E658" s="16"/>
     </row>
     <row r="659">
-      <c r="E659" s="17"/>
+      <c r="E659" s="16"/>
     </row>
     <row r="660">
-      <c r="E660" s="17"/>
+      <c r="E660" s="16"/>
     </row>
     <row r="661">
-      <c r="E661" s="17"/>
+      <c r="E661" s="16"/>
     </row>
     <row r="662">
-      <c r="E662" s="17"/>
+      <c r="E662" s="16"/>
     </row>
     <row r="663">
-      <c r="E663" s="17"/>
+      <c r="E663" s="16"/>
     </row>
     <row r="664">
-      <c r="E664" s="17"/>
+      <c r="E664" s="16"/>
     </row>
     <row r="665">
-      <c r="E665" s="17"/>
+      <c r="E665" s="16"/>
     </row>
     <row r="666">
-      <c r="E666" s="17"/>
+      <c r="E666" s="16"/>
     </row>
     <row r="667">
-      <c r="E667" s="17"/>
+      <c r="E667" s="16"/>
     </row>
     <row r="668">
-      <c r="E668" s="17"/>
+      <c r="E668" s="16"/>
     </row>
     <row r="669">
-      <c r="E669" s="17"/>
+      <c r="E669" s="16"/>
     </row>
     <row r="670">
-      <c r="E670" s="17"/>
+      <c r="E670" s="16"/>
     </row>
     <row r="671">
-      <c r="E671" s="17"/>
+      <c r="E671" s="16"/>
     </row>
     <row r="672">
-      <c r="E672" s="17"/>
+      <c r="E672" s="16"/>
     </row>
     <row r="673">
-      <c r="E673" s="17"/>
+      <c r="E673" s="16"/>
     </row>
     <row r="674">
-      <c r="E674" s="17"/>
+      <c r="E674" s="16"/>
     </row>
     <row r="675">
-      <c r="E675" s="17"/>
+      <c r="E675" s="16"/>
     </row>
     <row r="676">
-      <c r="E676" s="17"/>
+      <c r="E676" s="16"/>
     </row>
     <row r="677">
-      <c r="E677" s="17"/>
+      <c r="E677" s="16"/>
     </row>
     <row r="678">
-      <c r="E678" s="17"/>
+      <c r="E678" s="16"/>
     </row>
     <row r="679">
-      <c r="E679" s="17"/>
+      <c r="E679" s="16"/>
     </row>
     <row r="680">
-      <c r="E680" s="17"/>
+      <c r="E680" s="16"/>
     </row>
     <row r="681">
-      <c r="E681" s="17"/>
+      <c r="E681" s="16"/>
     </row>
     <row r="682">
-      <c r="E682" s="17"/>
+      <c r="E682" s="16"/>
     </row>
     <row r="683">
-      <c r="E683" s="17"/>
+      <c r="E683" s="16"/>
     </row>
     <row r="684">
-      <c r="E684" s="17"/>
+      <c r="E684" s="16"/>
     </row>
     <row r="685">
-      <c r="E685" s="17"/>
+      <c r="E685" s="16"/>
     </row>
     <row r="686">
-      <c r="E686" s="17"/>
+      <c r="E686" s="16"/>
     </row>
     <row r="687">
-      <c r="E687" s="17"/>
+      <c r="E687" s="16"/>
     </row>
     <row r="688">
-      <c r="E688" s="17"/>
+      <c r="E688" s="16"/>
     </row>
     <row r="689">
-      <c r="E689" s="17"/>
+      <c r="E689" s="16"/>
     </row>
     <row r="690">
-      <c r="E690" s="17"/>
+      <c r="E690" s="16"/>
     </row>
     <row r="691">
-      <c r="E691" s="17"/>
+      <c r="E691" s="16"/>
     </row>
     <row r="692">
-      <c r="E692" s="17"/>
+      <c r="E692" s="16"/>
     </row>
     <row r="693">
-      <c r="E693" s="17"/>
+      <c r="E693" s="16"/>
     </row>
     <row r="694">
-      <c r="E694" s="17"/>
+      <c r="E694" s="16"/>
     </row>
     <row r="695">
-      <c r="E695" s="17"/>
+      <c r="E695" s="16"/>
     </row>
     <row r="696">
-      <c r="E696" s="17"/>
+      <c r="E696" s="16"/>
     </row>
     <row r="697">
-      <c r="E697" s="17"/>
+      <c r="E697" s="16"/>
     </row>
     <row r="698">
-      <c r="E698" s="17"/>
+      <c r="E698" s="16"/>
     </row>
     <row r="699">
-      <c r="E699" s="17"/>
+      <c r="E699" s="16"/>
     </row>
     <row r="700">
-      <c r="E700" s="17"/>
+      <c r="E700" s="16"/>
     </row>
     <row r="701">
-      <c r="E701" s="17"/>
+      <c r="E701" s="16"/>
     </row>
     <row r="702">
-      <c r="E702" s="17"/>
+      <c r="E702" s="16"/>
     </row>
     <row r="703">
-      <c r="E703" s="17"/>
+      <c r="E703" s="16"/>
     </row>
     <row r="704">
-      <c r="E704" s="17"/>
+      <c r="E704" s="16"/>
     </row>
     <row r="705">
-      <c r="E705" s="17"/>
+      <c r="E705" s="16"/>
     </row>
     <row r="706">
-      <c r="E706" s="17"/>
+      <c r="E706" s="16"/>
     </row>
     <row r="707">
-      <c r="E707" s="17"/>
+      <c r="E707" s="16"/>
     </row>
     <row r="708">
-      <c r="E708" s="17"/>
+      <c r="E708" s="16"/>
     </row>
     <row r="709">
-      <c r="E709" s="17"/>
+      <c r="E709" s="16"/>
     </row>
     <row r="710">
-      <c r="E710" s="17"/>
+      <c r="E710" s="16"/>
     </row>
     <row r="711">
-      <c r="E711" s="17"/>
+      <c r="E711" s="16"/>
     </row>
     <row r="712">
-      <c r="E712" s="17"/>
+      <c r="E712" s="16"/>
     </row>
     <row r="713">
-      <c r="E713" s="17"/>
+      <c r="E713" s="16"/>
     </row>
     <row r="714">
-      <c r="E714" s="17"/>
+      <c r="E714" s="16"/>
     </row>
     <row r="715">
-      <c r="E715" s="17"/>
+      <c r="E715" s="16"/>
     </row>
     <row r="716">
-      <c r="E716" s="17"/>
+      <c r="E716" s="16"/>
     </row>
     <row r="717">
-      <c r="E717" s="17"/>
+      <c r="E717" s="16"/>
     </row>
     <row r="718">
-      <c r="E718" s="17"/>
+      <c r="E718" s="16"/>
     </row>
     <row r="719">
-      <c r="E719" s="17"/>
+      <c r="E719" s="16"/>
     </row>
     <row r="720">
-      <c r="E720" s="17"/>
+      <c r="E720" s="16"/>
     </row>
     <row r="721">
-      <c r="E721" s="17"/>
+      <c r="E721" s="16"/>
     </row>
     <row r="722">
-      <c r="E722" s="17"/>
+      <c r="E722" s="16"/>
     </row>
     <row r="723">
-      <c r="E723" s="17"/>
+      <c r="E723" s="16"/>
     </row>
     <row r="724">
-      <c r="E724" s="17"/>
+      <c r="E724" s="16"/>
     </row>
     <row r="725">
-      <c r="E725" s="17"/>
+      <c r="E725" s="16"/>
     </row>
     <row r="726">
-      <c r="E726" s="17"/>
+      <c r="E726" s="16"/>
     </row>
     <row r="727">
-      <c r="E727" s="17"/>
+      <c r="E727" s="16"/>
     </row>
     <row r="728">
-      <c r="E728" s="17"/>
+      <c r="E728" s="16"/>
     </row>
     <row r="729">
-      <c r="E729" s="17"/>
+      <c r="E729" s="16"/>
     </row>
     <row r="730">
-      <c r="E730" s="17"/>
+      <c r="E730" s="16"/>
     </row>
     <row r="731">
-      <c r="E731" s="17"/>
+      <c r="E731" s="16"/>
     </row>
     <row r="732">
-      <c r="E732" s="17"/>
+      <c r="E732" s="16"/>
     </row>
     <row r="733">
-      <c r="E733" s="17"/>
+      <c r="E733" s="16"/>
     </row>
     <row r="734">
-      <c r="E734" s="17"/>
+      <c r="E734" s="16"/>
     </row>
     <row r="735">
-      <c r="E735" s="17"/>
+      <c r="E735" s="16"/>
     </row>
     <row r="736">
-      <c r="E736" s="17"/>
+      <c r="E736" s="16"/>
     </row>
     <row r="737">
-      <c r="E737" s="17"/>
+      <c r="E737" s="16"/>
     </row>
     <row r="738">
-      <c r="E738" s="17"/>
+      <c r="E738" s="16"/>
     </row>
     <row r="739">
-      <c r="E739" s="17"/>
+      <c r="E739" s="16"/>
     </row>
     <row r="740">
-      <c r="E740" s="17"/>
+      <c r="E740" s="16"/>
     </row>
     <row r="741">
-      <c r="E741" s="17"/>
+      <c r="E741" s="16"/>
     </row>
     <row r="742">
-      <c r="E742" s="17"/>
+      <c r="E742" s="16"/>
     </row>
     <row r="743">
-      <c r="E743" s="17"/>
+      <c r="E743" s="16"/>
     </row>
     <row r="744">
-      <c r="E744" s="17"/>
+      <c r="E744" s="16"/>
     </row>
     <row r="745">
-      <c r="E745" s="17"/>
+      <c r="E745" s="16"/>
     </row>
     <row r="746">
-      <c r="E746" s="17"/>
+      <c r="E746" s="16"/>
     </row>
     <row r="747">
-      <c r="E747" s="17"/>
+      <c r="E747" s="16"/>
     </row>
     <row r="748">
-      <c r="E748" s="17"/>
+      <c r="E748" s="16"/>
     </row>
     <row r="749">
-      <c r="E749" s="17"/>
+      <c r="E749" s="16"/>
     </row>
     <row r="750">
-      <c r="E750" s="17"/>
+      <c r="E750" s="16"/>
     </row>
     <row r="751">
-      <c r="E751" s="17"/>
+      <c r="E751" s="16"/>
     </row>
     <row r="752">
-      <c r="E752" s="17"/>
+      <c r="E752" s="16"/>
     </row>
     <row r="753">
-      <c r="E753" s="17"/>
+      <c r="E753" s="16"/>
     </row>
     <row r="754">
-      <c r="E754" s="17"/>
+      <c r="E754" s="16"/>
     </row>
     <row r="755">
-      <c r="E755" s="17"/>
+      <c r="E755" s="16"/>
     </row>
     <row r="756">
-      <c r="E756" s="17"/>
+      <c r="E756" s="16"/>
     </row>
     <row r="757">
-      <c r="E757" s="17"/>
+      <c r="E757" s="16"/>
     </row>
     <row r="758">
-      <c r="E758" s="17"/>
+      <c r="E758" s="16"/>
     </row>
     <row r="759">
-      <c r="E759" s="17"/>
+      <c r="E759" s="16"/>
     </row>
     <row r="760">
-      <c r="E760" s="17"/>
+      <c r="E760" s="16"/>
     </row>
     <row r="761">
-      <c r="E761" s="17"/>
+      <c r="E761" s="16"/>
     </row>
     <row r="762">
-      <c r="E762" s="17"/>
+      <c r="E762" s="16"/>
     </row>
     <row r="763">
-      <c r="E763" s="17"/>
+      <c r="E763" s="16"/>
     </row>
     <row r="764">
-      <c r="E764" s="17"/>
+      <c r="E764" s="16"/>
     </row>
     <row r="765">
-      <c r="E765" s="17"/>
+      <c r="E765" s="16"/>
     </row>
     <row r="766">
-      <c r="E766" s="17"/>
+      <c r="E766" s="16"/>
     </row>
     <row r="767">
-      <c r="E767" s="17"/>
+      <c r="E767" s="16"/>
     </row>
     <row r="768">
-      <c r="E768" s="17"/>
+      <c r="E768" s="16"/>
     </row>
     <row r="769">
-      <c r="E769" s="17"/>
+      <c r="E769" s="16"/>
     </row>
     <row r="770">
-      <c r="E770" s="17"/>
+      <c r="E770" s="16"/>
     </row>
     <row r="771">
-      <c r="E771" s="17"/>
+      <c r="E771" s="16"/>
     </row>
     <row r="772">
-      <c r="E772" s="17"/>
+      <c r="E772" s="16"/>
     </row>
     <row r="773">
-      <c r="E773" s="17"/>
+      <c r="E773" s="16"/>
     </row>
     <row r="774">
-      <c r="E774" s="17"/>
+      <c r="E774" s="16"/>
     </row>
     <row r="775">
-      <c r="E775" s="17"/>
+      <c r="E775" s="16"/>
     </row>
     <row r="776">
-      <c r="E776" s="17"/>
+      <c r="E776" s="16"/>
     </row>
     <row r="777">
-      <c r="E777" s="17"/>
+      <c r="E777" s="16"/>
     </row>
     <row r="778">
-      <c r="E778" s="17"/>
+      <c r="E778" s="16"/>
     </row>
     <row r="779">
-      <c r="E779" s="17"/>
+      <c r="E779" s="16"/>
     </row>
     <row r="780">
-      <c r="E780" s="17"/>
+      <c r="E780" s="16"/>
     </row>
     <row r="781">
-      <c r="E781" s="17"/>
+      <c r="E781" s="16"/>
     </row>
     <row r="782">
-      <c r="E782" s="17"/>
+      <c r="E782" s="16"/>
     </row>
     <row r="783">
-      <c r="E783" s="17"/>
+      <c r="E783" s="16"/>
     </row>
     <row r="784">
-      <c r="E784" s="17"/>
+      <c r="E784" s="16"/>
     </row>
     <row r="785">
-      <c r="E785" s="17"/>
+      <c r="E785" s="16"/>
     </row>
     <row r="786">
-      <c r="E786" s="17"/>
+      <c r="E786" s="16"/>
     </row>
     <row r="787">
-      <c r="E787" s="17"/>
+      <c r="E787" s="16"/>
     </row>
     <row r="788">
-      <c r="E788" s="17"/>
+      <c r="E788" s="16"/>
     </row>
     <row r="789">
-      <c r="E789" s="17"/>
+      <c r="E789" s="16"/>
     </row>
     <row r="790">
-      <c r="E790" s="17"/>
+      <c r="E790" s="16"/>
     </row>
     <row r="791">
-      <c r="E791" s="17"/>
+      <c r="E791" s="16"/>
     </row>
     <row r="792">
-      <c r="E792" s="17"/>
+      <c r="E792" s="16"/>
     </row>
     <row r="793">
-      <c r="E793" s="17"/>
+      <c r="E793" s="16"/>
     </row>
     <row r="794">
-      <c r="E794" s="17"/>
+      <c r="E794" s="16"/>
     </row>
     <row r="795">
-      <c r="E795" s="17"/>
+      <c r="E795" s="16"/>
     </row>
     <row r="796">
-      <c r="E796" s="17"/>
+      <c r="E796" s="16"/>
     </row>
     <row r="797">
-      <c r="E797" s="17"/>
+      <c r="E797" s="16"/>
     </row>
     <row r="798">
-      <c r="E798" s="17"/>
+      <c r="E798" s="16"/>
     </row>
     <row r="799">
-      <c r="E799" s="17"/>
+      <c r="E799" s="16"/>
     </row>
     <row r="800">
-      <c r="E800" s="17"/>
+      <c r="E800" s="16"/>
     </row>
     <row r="801">
-      <c r="E801" s="17"/>
+      <c r="E801" s="16"/>
     </row>
     <row r="802">
-      <c r="E802" s="17"/>
+      <c r="E802" s="16"/>
     </row>
     <row r="803">
-      <c r="E803" s="17"/>
+      <c r="E803" s="16"/>
     </row>
     <row r="804">
-      <c r="E804" s="17"/>
+      <c r="E804" s="16"/>
     </row>
     <row r="805">
-      <c r="E805" s="17"/>
+      <c r="E805" s="16"/>
     </row>
     <row r="806">
-      <c r="E806" s="17"/>
+      <c r="E806" s="16"/>
     </row>
     <row r="807">
-      <c r="E807" s="17"/>
+      <c r="E807" s="16"/>
     </row>
     <row r="808">
-      <c r="E808" s="17"/>
+      <c r="E808" s="16"/>
     </row>
     <row r="809">
-      <c r="E809" s="17"/>
+      <c r="E809" s="16"/>
     </row>
     <row r="810">
-      <c r="E810" s="17"/>
+      <c r="E810" s="16"/>
     </row>
     <row r="811">
-      <c r="E811" s="17"/>
+      <c r="E811" s="16"/>
     </row>
     <row r="812">
-      <c r="E812" s="17"/>
+      <c r="E812" s="16"/>
     </row>
     <row r="813">
-      <c r="E813" s="17"/>
+      <c r="E813" s="16"/>
     </row>
     <row r="814">
-      <c r="E814" s="17"/>
+      <c r="E814" s="16"/>
     </row>
     <row r="815">
-      <c r="E815" s="17"/>
+      <c r="E815" s="16"/>
     </row>
     <row r="816">
-      <c r="E816" s="17"/>
+      <c r="E816" s="16"/>
     </row>
     <row r="817">
-      <c r="E817" s="17"/>
+      <c r="E817" s="16"/>
     </row>
     <row r="818">
-      <c r="E818" s="17"/>
+      <c r="E818" s="16"/>
     </row>
     <row r="819">
-      <c r="E819" s="17"/>
+      <c r="E819" s="16"/>
     </row>
     <row r="820">
-      <c r="E820" s="17"/>
+      <c r="E820" s="16"/>
     </row>
     <row r="821">
-      <c r="E821" s="17"/>
+      <c r="E821" s="16"/>
     </row>
     <row r="822">
-      <c r="E822" s="17"/>
+      <c r="E822" s="16"/>
     </row>
     <row r="823">
-      <c r="E823" s="17"/>
+      <c r="E823" s="16"/>
     </row>
     <row r="824">
-      <c r="E824" s="17"/>
+      <c r="E824" s="16"/>
     </row>
     <row r="825">
-      <c r="E825" s="17"/>
+      <c r="E825" s="16"/>
     </row>
     <row r="826">
-      <c r="E826" s="17"/>
+      <c r="E826" s="16"/>
     </row>
     <row r="827">
-      <c r="E827" s="17"/>
+      <c r="E827" s="16"/>
     </row>
     <row r="828">
-      <c r="E828" s="17"/>
+      <c r="E828" s="16"/>
     </row>
     <row r="829">
-      <c r="E829" s="17"/>
+      <c r="E829" s="16"/>
     </row>
     <row r="830">
-      <c r="E830" s="17"/>
+      <c r="E830" s="16"/>
     </row>
     <row r="831">
-      <c r="E831" s="17"/>
+      <c r="E831" s="16"/>
     </row>
     <row r="832">
-      <c r="E832" s="17"/>
+      <c r="E832" s="16"/>
     </row>
     <row r="833">
-      <c r="E833" s="17"/>
+      <c r="E833" s="16"/>
     </row>
     <row r="834">
-      <c r="E834" s="17"/>
+      <c r="E834" s="16"/>
     </row>
     <row r="835">
-      <c r="E835" s="17"/>
+      <c r="E835" s="16"/>
     </row>
     <row r="836">
-      <c r="E836" s="17"/>
+      <c r="E836" s="16"/>
     </row>
     <row r="837">
-      <c r="E837" s="17"/>
+      <c r="E837" s="16"/>
     </row>
     <row r="838">
-      <c r="E838" s="17"/>
+      <c r="E838" s="16"/>
     </row>
     <row r="839">
-      <c r="E839" s="17"/>
+      <c r="E839" s="16"/>
     </row>
     <row r="840">
-      <c r="E840" s="17"/>
+      <c r="E840" s="16"/>
     </row>
     <row r="841">
-      <c r="E841" s="17"/>
+      <c r="E841" s="16"/>
     </row>
     <row r="842">
-      <c r="E842" s="17"/>
+      <c r="E842" s="16"/>
     </row>
     <row r="843">
-      <c r="E843" s="17"/>
+      <c r="E843" s="16"/>
     </row>
     <row r="844">
-      <c r="E844" s="17"/>
+      <c r="E844" s="16"/>
     </row>
     <row r="845">
-      <c r="E845" s="17"/>
+      <c r="E845" s="16"/>
     </row>
     <row r="846">
-      <c r="E846" s="17"/>
+      <c r="E846" s="16"/>
     </row>
     <row r="847">
-      <c r="E847" s="17"/>
+      <c r="E847" s="16"/>
     </row>
     <row r="848">
-      <c r="E848" s="17"/>
+      <c r="E848" s="16"/>
     </row>
     <row r="849">
-      <c r="E849" s="17"/>
+      <c r="E849" s="16"/>
     </row>
     <row r="850">
-      <c r="E850" s="17"/>
+      <c r="E850" s="16"/>
     </row>
     <row r="851">
-      <c r="E851" s="17"/>
+      <c r="E851" s="16"/>
     </row>
     <row r="852">
-      <c r="E852" s="17"/>
+      <c r="E852" s="16"/>
     </row>
     <row r="853">
-      <c r="E853" s="17"/>
+      <c r="E853" s="16"/>
     </row>
     <row r="854">
-      <c r="E854" s="17"/>
+      <c r="E854" s="16"/>
     </row>
     <row r="855">
-      <c r="E855" s="17"/>
+      <c r="E855" s="16"/>
     </row>
     <row r="856">
-      <c r="E856" s="17"/>
+      <c r="E856" s="16"/>
     </row>
     <row r="857">
-      <c r="E857" s="17"/>
+      <c r="E857" s="16"/>
     </row>
     <row r="858">
-      <c r="E858" s="17"/>
+      <c r="E858" s="16"/>
     </row>
     <row r="859">
-      <c r="E859" s="17"/>
+      <c r="E859" s="16"/>
     </row>
     <row r="860">
-      <c r="E860" s="17"/>
+      <c r="E860" s="16"/>
     </row>
     <row r="861">
-      <c r="E861" s="17"/>
+      <c r="E861" s="16"/>
     </row>
     <row r="862">
-      <c r="E862" s="17"/>
+      <c r="E862" s="16"/>
     </row>
     <row r="863">
-      <c r="E863" s="17"/>
+      <c r="E863" s="16"/>
     </row>
     <row r="864">
-      <c r="E864" s="17"/>
+      <c r="E864" s="16"/>
     </row>
     <row r="865">
-      <c r="E865" s="17"/>
+      <c r="E865" s="16"/>
     </row>
     <row r="866">
-      <c r="E866" s="17"/>
+      <c r="E866" s="16"/>
     </row>
     <row r="867">
-      <c r="E867" s="17"/>
+      <c r="E867" s="16"/>
     </row>
     <row r="868">
-      <c r="E868" s="17"/>
+      <c r="E868" s="16"/>
     </row>
     <row r="869">
-      <c r="E869" s="17"/>
+      <c r="E869" s="16"/>
     </row>
     <row r="870">
-      <c r="E870" s="17"/>
+      <c r="E870" s="16"/>
     </row>
     <row r="871">
-      <c r="E871" s="17"/>
+      <c r="E871" s="16"/>
     </row>
     <row r="872">
-      <c r="E872" s="17"/>
+      <c r="E872" s="16"/>
     </row>
     <row r="873">
-      <c r="E873" s="17"/>
+      <c r="E873" s="16"/>
     </row>
     <row r="874">
-      <c r="E874" s="17"/>
+      <c r="E874" s="16"/>
     </row>
     <row r="875">
-      <c r="E875" s="17"/>
+      <c r="E875" s="16"/>
     </row>
     <row r="876">
-      <c r="E876" s="17"/>
+      <c r="E876" s="16"/>
     </row>
     <row r="877">
-      <c r="E877" s="17"/>
+      <c r="E877" s="16"/>
     </row>
     <row r="878">
-      <c r="E878" s="17"/>
+      <c r="E878" s="16"/>
     </row>
     <row r="879">
-      <c r="E879" s="17"/>
+      <c r="E879" s="16"/>
     </row>
     <row r="880">
-      <c r="E880" s="17"/>
+      <c r="E880" s="16"/>
     </row>
     <row r="881">
-      <c r="E881" s="17"/>
+      <c r="E881" s="16"/>
     </row>
     <row r="882">
-      <c r="E882" s="17"/>
+      <c r="E882" s="16"/>
     </row>
     <row r="883">
-      <c r="E883" s="17"/>
+      <c r="E883" s="16"/>
     </row>
     <row r="884">
-      <c r="E884" s="17"/>
+      <c r="E884" s="16"/>
     </row>
     <row r="885">
-      <c r="E885" s="17"/>
+      <c r="E885" s="16"/>
     </row>
     <row r="886">
-      <c r="E886" s="17"/>
+      <c r="E886" s="16"/>
     </row>
     <row r="887">
-      <c r="E887" s="17"/>
+      <c r="E887" s="16"/>
     </row>
     <row r="888">
-      <c r="E888" s="17"/>
+      <c r="E888" s="16"/>
     </row>
     <row r="889">
-      <c r="E889" s="17"/>
+      <c r="E889" s="16"/>
     </row>
     <row r="890">
-      <c r="E890" s="17"/>
+      <c r="E890" s="16"/>
     </row>
     <row r="891">
-      <c r="E891" s="17"/>
+      <c r="E891" s="16"/>
     </row>
     <row r="892">
-      <c r="E892" s="17"/>
+      <c r="E892" s="16"/>
     </row>
     <row r="893">
-      <c r="E893" s="17"/>
+      <c r="E893" s="16"/>
     </row>
     <row r="894">
-      <c r="E894" s="17"/>
+      <c r="E894" s="16"/>
     </row>
     <row r="895">
-      <c r="E895" s="17"/>
+      <c r="E895" s="16"/>
     </row>
     <row r="896">
-      <c r="E896" s="17"/>
+      <c r="E896" s="16"/>
     </row>
     <row r="897">
-      <c r="E897" s="17"/>
+      <c r="E897" s="16"/>
     </row>
     <row r="898">
-      <c r="E898" s="17"/>
+      <c r="E898" s="16"/>
     </row>
     <row r="899">
-      <c r="E899" s="17"/>
+      <c r="E899" s="16"/>
     </row>
     <row r="900">
-      <c r="E900" s="17"/>
+      <c r="E900" s="16"/>
     </row>
     <row r="901">
-      <c r="E901" s="17"/>
+      <c r="E901" s="16"/>
     </row>
     <row r="902">
-      <c r="E902" s="17"/>
+      <c r="E902" s="16"/>
     </row>
     <row r="903">
-      <c r="E903" s="17"/>
+      <c r="E903" s="16"/>
     </row>
     <row r="904">
-      <c r="E904" s="17"/>
+      <c r="E904" s="16"/>
     </row>
     <row r="905">
-      <c r="E905" s="17"/>
+      <c r="E905" s="16"/>
     </row>
     <row r="906">
-      <c r="E906" s="17"/>
+      <c r="E906" s="16"/>
     </row>
     <row r="907">
-      <c r="E907" s="17"/>
+      <c r="E907" s="16"/>
     </row>
     <row r="908">
-      <c r="E908" s="17"/>
+      <c r="E908" s="16"/>
     </row>
     <row r="909">
-      <c r="E909" s="17"/>
+      <c r="E909" s="16"/>
     </row>
     <row r="910">
-      <c r="E910" s="17"/>
+      <c r="E910" s="16"/>
     </row>
     <row r="911">
-      <c r="E911" s="17"/>
+      <c r="E911" s="16"/>
     </row>
     <row r="912">
-      <c r="E912" s="17"/>
+      <c r="E912" s="16"/>
     </row>
     <row r="913">
-      <c r="E913" s="17"/>
+      <c r="E913" s="16"/>
     </row>
     <row r="914">
-      <c r="E914" s="17"/>
+      <c r="E914" s="16"/>
     </row>
     <row r="915">
-      <c r="E915" s="17"/>
+      <c r="E915" s="16"/>
     </row>
     <row r="916">
-      <c r="E916" s="17"/>
+      <c r="E916" s="16"/>
     </row>
     <row r="917">
-      <c r="E917" s="17"/>
+      <c r="E917" s="16"/>
     </row>
     <row r="918">
-      <c r="E918" s="17"/>
+      <c r="E918" s="16"/>
     </row>
     <row r="919">
-      <c r="E919" s="17"/>
+      <c r="E919" s="16"/>
     </row>
     <row r="920">
-      <c r="E920" s="17"/>
+      <c r="E920" s="16"/>
     </row>
     <row r="921">
-      <c r="E921" s="17"/>
+      <c r="E921" s="16"/>
     </row>
     <row r="922">
-      <c r="E922" s="17"/>
+      <c r="E922" s="16"/>
     </row>
     <row r="923">
-      <c r="E923" s="17"/>
+      <c r="E923" s="16"/>
     </row>
     <row r="924">
-      <c r="E924" s="17"/>
+      <c r="E924" s="16"/>
     </row>
     <row r="925">
-      <c r="E925" s="17"/>
+      <c r="E925" s="16"/>
     </row>
     <row r="926">
-      <c r="E926" s="17"/>
+      <c r="E926" s="16"/>
     </row>
     <row r="927">
-      <c r="E927" s="17"/>
+      <c r="E927" s="16"/>
     </row>
   </sheetData>
   <hyperlinks>
